--- a/output/version3/test/20-15/MARL/CTDE/RL-RL with EP (+comm)/(RL+RL) test results.xlsx
+++ b/output/version3/test/20-15/MARL/CTDE/RL-RL with EP (+comm)/(RL+RL) test results.xlsx
@@ -471,37 +471,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>822</v>
+        <v>987</v>
       </c>
       <c r="C2" t="n">
-        <v>754</v>
+        <v>809</v>
       </c>
       <c r="D2" t="n">
-        <v>981</v>
+        <v>845</v>
       </c>
       <c r="E2" t="n">
-        <v>892</v>
+        <v>854</v>
       </c>
       <c r="F2" t="n">
-        <v>992</v>
+        <v>825</v>
       </c>
       <c r="G2" t="n">
-        <v>984</v>
+        <v>876</v>
       </c>
       <c r="H2" t="n">
-        <v>900</v>
+        <v>865</v>
       </c>
       <c r="I2" t="n">
-        <v>892</v>
+        <v>798</v>
       </c>
       <c r="J2" t="n">
-        <v>869</v>
+        <v>816</v>
       </c>
       <c r="K2" t="n">
-        <v>863</v>
+        <v>838</v>
       </c>
       <c r="L2" t="n">
-        <v>894.9</v>
+        <v>851.3</v>
       </c>
     </row>
     <row r="3">
@@ -509,37 +509,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>820</v>
+        <v>941</v>
       </c>
       <c r="C3" t="n">
-        <v>978</v>
+        <v>827</v>
       </c>
       <c r="D3" t="n">
-        <v>925</v>
+        <v>858</v>
       </c>
       <c r="E3" t="n">
-        <v>891</v>
+        <v>825</v>
       </c>
       <c r="F3" t="n">
-        <v>901</v>
+        <v>852</v>
       </c>
       <c r="G3" t="n">
-        <v>896</v>
+        <v>853</v>
       </c>
       <c r="H3" t="n">
-        <v>882</v>
+        <v>862</v>
       </c>
       <c r="I3" t="n">
-        <v>891</v>
+        <v>952</v>
       </c>
       <c r="J3" t="n">
-        <v>882</v>
+        <v>865</v>
       </c>
       <c r="K3" t="n">
-        <v>1130</v>
+        <v>876</v>
       </c>
       <c r="L3" t="n">
-        <v>919.6</v>
+        <v>871.1</v>
       </c>
     </row>
     <row r="4">
@@ -547,37 +547,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>824</v>
+        <v>903</v>
       </c>
       <c r="C4" t="n">
-        <v>745</v>
+        <v>831</v>
       </c>
       <c r="D4" t="n">
-        <v>1007</v>
+        <v>946</v>
       </c>
       <c r="E4" t="n">
-        <v>882</v>
+        <v>871</v>
       </c>
       <c r="F4" t="n">
-        <v>803</v>
+        <v>881</v>
       </c>
       <c r="G4" t="n">
-        <v>853</v>
+        <v>957</v>
       </c>
       <c r="H4" t="n">
-        <v>1006</v>
+        <v>809</v>
       </c>
       <c r="I4" t="n">
-        <v>908</v>
+        <v>980</v>
       </c>
       <c r="J4" t="n">
-        <v>855</v>
+        <v>967</v>
       </c>
       <c r="K4" t="n">
-        <v>1012</v>
+        <v>869</v>
       </c>
       <c r="L4" t="n">
-        <v>889.5</v>
+        <v>901.4</v>
       </c>
     </row>
     <row r="5">
@@ -585,37 +585,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>942</v>
+        <v>819</v>
       </c>
       <c r="C5" t="n">
-        <v>794</v>
+        <v>818</v>
       </c>
       <c r="D5" t="n">
-        <v>896</v>
+        <v>819</v>
       </c>
       <c r="E5" t="n">
-        <v>966</v>
+        <v>878</v>
       </c>
       <c r="F5" t="n">
+        <v>895</v>
+      </c>
+      <c r="G5" t="n">
+        <v>909</v>
+      </c>
+      <c r="H5" t="n">
+        <v>836</v>
+      </c>
+      <c r="I5" t="n">
         <v>874</v>
       </c>
-      <c r="G5" t="n">
-        <v>756</v>
-      </c>
-      <c r="H5" t="n">
-        <v>927</v>
-      </c>
-      <c r="I5" t="n">
-        <v>756</v>
-      </c>
       <c r="J5" t="n">
-        <v>810</v>
+        <v>852</v>
       </c>
       <c r="K5" t="n">
-        <v>841</v>
+        <v>833</v>
       </c>
       <c r="L5" t="n">
-        <v>856.2</v>
+        <v>853.3</v>
       </c>
     </row>
     <row r="6">
@@ -623,37 +623,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>720</v>
+        <v>712</v>
       </c>
       <c r="C6" t="n">
+        <v>748</v>
+      </c>
+      <c r="D6" t="n">
+        <v>769</v>
+      </c>
+      <c r="E6" t="n">
+        <v>779</v>
+      </c>
+      <c r="F6" t="n">
+        <v>750</v>
+      </c>
+      <c r="G6" t="n">
+        <v>782</v>
+      </c>
+      <c r="H6" t="n">
+        <v>722</v>
+      </c>
+      <c r="I6" t="n">
+        <v>823</v>
+      </c>
+      <c r="J6" t="n">
         <v>713</v>
       </c>
-      <c r="D6" t="n">
-        <v>665</v>
-      </c>
-      <c r="E6" t="n">
-        <v>707</v>
-      </c>
-      <c r="F6" t="n">
-        <v>716</v>
-      </c>
-      <c r="G6" t="n">
-        <v>769</v>
-      </c>
-      <c r="H6" t="n">
-        <v>675</v>
-      </c>
-      <c r="I6" t="n">
-        <v>778</v>
-      </c>
-      <c r="J6" t="n">
-        <v>683</v>
-      </c>
       <c r="K6" t="n">
-        <v>700</v>
+        <v>795</v>
       </c>
       <c r="L6" t="n">
-        <v>712.6</v>
+        <v>759.3</v>
       </c>
     </row>
     <row r="7">
@@ -661,37 +661,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>891</v>
+        <v>872</v>
       </c>
       <c r="C7" t="n">
-        <v>1032</v>
+        <v>888</v>
       </c>
       <c r="D7" t="n">
-        <v>833</v>
+        <v>872</v>
       </c>
       <c r="E7" t="n">
-        <v>1027</v>
+        <v>866</v>
       </c>
       <c r="F7" t="n">
-        <v>1040</v>
+        <v>831</v>
       </c>
       <c r="G7" t="n">
-        <v>934</v>
+        <v>998</v>
       </c>
       <c r="H7" t="n">
-        <v>918</v>
+        <v>858</v>
       </c>
       <c r="I7" t="n">
-        <v>891</v>
+        <v>898</v>
       </c>
       <c r="J7" t="n">
-        <v>864</v>
+        <v>920</v>
       </c>
       <c r="K7" t="n">
-        <v>841</v>
+        <v>835</v>
       </c>
       <c r="L7" t="n">
-        <v>927.1</v>
+        <v>883.8</v>
       </c>
     </row>
     <row r="8">
@@ -699,37 +699,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>903</v>
+        <v>806</v>
       </c>
       <c r="C8" t="n">
-        <v>798</v>
+        <v>901</v>
       </c>
       <c r="D8" t="n">
-        <v>973</v>
+        <v>908</v>
       </c>
       <c r="E8" t="n">
-        <v>800</v>
+        <v>925</v>
       </c>
       <c r="F8" t="n">
-        <v>940</v>
+        <v>821</v>
       </c>
       <c r="G8" t="n">
-        <v>839</v>
+        <v>886</v>
       </c>
       <c r="H8" t="n">
-        <v>911</v>
+        <v>736</v>
       </c>
       <c r="I8" t="n">
-        <v>1067</v>
+        <v>807</v>
       </c>
       <c r="J8" t="n">
-        <v>941</v>
+        <v>892</v>
       </c>
       <c r="K8" t="n">
-        <v>805</v>
+        <v>850</v>
       </c>
       <c r="L8" t="n">
-        <v>897.7</v>
+        <v>853.2</v>
       </c>
     </row>
     <row r="9">
@@ -737,37 +737,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>804</v>
+        <v>844</v>
       </c>
       <c r="C9" t="n">
-        <v>925</v>
+        <v>837</v>
       </c>
       <c r="D9" t="n">
-        <v>800</v>
+        <v>826</v>
       </c>
       <c r="E9" t="n">
-        <v>769</v>
+        <v>889</v>
       </c>
       <c r="F9" t="n">
-        <v>948</v>
+        <v>874</v>
       </c>
       <c r="G9" t="n">
-        <v>831</v>
+        <v>877</v>
       </c>
       <c r="H9" t="n">
-        <v>865</v>
+        <v>966</v>
       </c>
       <c r="I9" t="n">
-        <v>816</v>
+        <v>938</v>
       </c>
       <c r="J9" t="n">
-        <v>782</v>
+        <v>907</v>
       </c>
       <c r="K9" t="n">
-        <v>807</v>
+        <v>828</v>
       </c>
       <c r="L9" t="n">
-        <v>834.7</v>
+        <v>878.6</v>
       </c>
     </row>
     <row r="10">
@@ -775,37 +775,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>828</v>
+        <v>942</v>
       </c>
       <c r="C10" t="n">
-        <v>783</v>
+        <v>826</v>
       </c>
       <c r="D10" t="n">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="E10" t="n">
-        <v>752</v>
+        <v>954</v>
       </c>
       <c r="F10" t="n">
-        <v>764</v>
+        <v>750</v>
       </c>
       <c r="G10" t="n">
-        <v>904</v>
+        <v>768</v>
       </c>
       <c r="H10" t="n">
-        <v>901</v>
+        <v>739</v>
       </c>
       <c r="I10" t="n">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="J10" t="n">
-        <v>819</v>
+        <v>853</v>
       </c>
       <c r="K10" t="n">
-        <v>1022</v>
+        <v>772</v>
       </c>
       <c r="L10" t="n">
-        <v>851.4</v>
+        <v>834.4</v>
       </c>
     </row>
     <row r="11">
@@ -813,37 +813,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>888</v>
+        <v>959</v>
       </c>
       <c r="C11" t="n">
-        <v>973</v>
+        <v>876</v>
       </c>
       <c r="D11" t="n">
-        <v>815</v>
+        <v>797</v>
       </c>
       <c r="E11" t="n">
-        <v>815</v>
+        <v>894</v>
       </c>
       <c r="F11" t="n">
-        <v>819</v>
+        <v>791</v>
       </c>
       <c r="G11" t="n">
-        <v>858</v>
+        <v>981</v>
       </c>
       <c r="H11" t="n">
-        <v>831</v>
+        <v>948</v>
       </c>
       <c r="I11" t="n">
-        <v>925</v>
+        <v>821</v>
       </c>
       <c r="J11" t="n">
-        <v>885</v>
+        <v>994</v>
       </c>
       <c r="K11" t="n">
-        <v>830</v>
+        <v>954</v>
       </c>
       <c r="L11" t="n">
-        <v>863.9</v>
+        <v>901.5</v>
       </c>
     </row>
     <row r="12">
@@ -851,37 +851,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>966</v>
+        <v>759</v>
       </c>
       <c r="C12" t="n">
-        <v>937</v>
+        <v>975</v>
       </c>
       <c r="D12" t="n">
-        <v>960</v>
+        <v>888</v>
       </c>
       <c r="E12" t="n">
-        <v>898</v>
+        <v>864</v>
       </c>
       <c r="F12" t="n">
-        <v>916</v>
+        <v>838</v>
       </c>
       <c r="G12" t="n">
-        <v>755</v>
+        <v>876</v>
       </c>
       <c r="H12" t="n">
-        <v>850</v>
+        <v>790</v>
       </c>
       <c r="I12" t="n">
-        <v>859</v>
+        <v>835</v>
       </c>
       <c r="J12" t="n">
-        <v>1009</v>
+        <v>769</v>
       </c>
       <c r="K12" t="n">
-        <v>952</v>
+        <v>854</v>
       </c>
       <c r="L12" t="n">
-        <v>910.2</v>
+        <v>844.8</v>
       </c>
     </row>
     <row r="13">
@@ -889,37 +889,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>786</v>
+        <v>742</v>
       </c>
       <c r="C13" t="n">
-        <v>732</v>
+        <v>762</v>
       </c>
       <c r="D13" t="n">
-        <v>748</v>
+        <v>866</v>
       </c>
       <c r="E13" t="n">
-        <v>772</v>
+        <v>751</v>
       </c>
       <c r="F13" t="n">
-        <v>690</v>
+        <v>815</v>
       </c>
       <c r="G13" t="n">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="H13" t="n">
-        <v>803</v>
+        <v>862</v>
       </c>
       <c r="I13" t="n">
-        <v>796</v>
+        <v>763</v>
       </c>
       <c r="J13" t="n">
-        <v>865</v>
+        <v>913</v>
       </c>
       <c r="K13" t="n">
-        <v>698</v>
+        <v>733</v>
       </c>
       <c r="L13" t="n">
-        <v>769.1</v>
+        <v>800.9</v>
       </c>
     </row>
     <row r="14">
@@ -927,37 +927,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>813</v>
+        <v>941</v>
       </c>
       <c r="C14" t="n">
-        <v>975</v>
+        <v>863</v>
       </c>
       <c r="D14" t="n">
-        <v>791</v>
+        <v>822</v>
       </c>
       <c r="E14" t="n">
-        <v>776</v>
+        <v>908</v>
       </c>
       <c r="F14" t="n">
-        <v>829</v>
+        <v>843</v>
       </c>
       <c r="G14" t="n">
-        <v>912</v>
+        <v>839</v>
       </c>
       <c r="H14" t="n">
-        <v>815</v>
+        <v>837</v>
       </c>
       <c r="I14" t="n">
-        <v>868</v>
+        <v>789</v>
       </c>
       <c r="J14" t="n">
-        <v>848</v>
+        <v>995</v>
       </c>
       <c r="K14" t="n">
-        <v>926</v>
+        <v>960</v>
       </c>
       <c r="L14" t="n">
-        <v>855.3</v>
+        <v>879.7</v>
       </c>
     </row>
     <row r="15">
@@ -965,37 +965,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>843</v>
+        <v>876</v>
       </c>
       <c r="C15" t="n">
-        <v>671</v>
+        <v>788</v>
       </c>
       <c r="D15" t="n">
-        <v>847</v>
+        <v>914</v>
       </c>
       <c r="E15" t="n">
-        <v>818</v>
+        <v>941</v>
       </c>
       <c r="F15" t="n">
-        <v>809</v>
+        <v>846</v>
       </c>
       <c r="G15" t="n">
-        <v>881</v>
+        <v>861</v>
       </c>
       <c r="H15" t="n">
-        <v>834</v>
+        <v>762</v>
       </c>
       <c r="I15" t="n">
-        <v>805</v>
+        <v>895</v>
       </c>
       <c r="J15" t="n">
-        <v>825</v>
+        <v>840</v>
       </c>
       <c r="K15" t="n">
-        <v>820</v>
+        <v>859</v>
       </c>
       <c r="L15" t="n">
-        <v>815.3</v>
+        <v>858.2</v>
       </c>
     </row>
     <row r="16">
@@ -1003,37 +1003,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>879</v>
+        <v>874</v>
       </c>
       <c r="C16" t="n">
-        <v>921</v>
+        <v>896</v>
       </c>
       <c r="D16" t="n">
-        <v>839</v>
+        <v>1186</v>
       </c>
       <c r="E16" t="n">
-        <v>1018</v>
+        <v>1134</v>
       </c>
       <c r="F16" t="n">
-        <v>866</v>
+        <v>971</v>
       </c>
       <c r="G16" t="n">
-        <v>961</v>
+        <v>855</v>
       </c>
       <c r="H16" t="n">
-        <v>893</v>
+        <v>899</v>
       </c>
       <c r="I16" t="n">
-        <v>836</v>
+        <v>905</v>
       </c>
       <c r="J16" t="n">
-        <v>925</v>
+        <v>889</v>
       </c>
       <c r="K16" t="n">
-        <v>1003</v>
+        <v>889</v>
       </c>
       <c r="L16" t="n">
-        <v>914.1</v>
+        <v>949.8</v>
       </c>
     </row>
     <row r="17">
@@ -1041,37 +1041,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>920</v>
+        <v>961</v>
       </c>
       <c r="C17" t="n">
-        <v>977</v>
+        <v>966</v>
       </c>
       <c r="D17" t="n">
-        <v>872</v>
+        <v>829</v>
       </c>
       <c r="E17" t="n">
-        <v>1008</v>
+        <v>825</v>
       </c>
       <c r="F17" t="n">
-        <v>864</v>
+        <v>857</v>
       </c>
       <c r="G17" t="n">
-        <v>893</v>
+        <v>857</v>
       </c>
       <c r="H17" t="n">
-        <v>872</v>
+        <v>1007</v>
       </c>
       <c r="I17" t="n">
-        <v>1015</v>
+        <v>1021</v>
       </c>
       <c r="J17" t="n">
-        <v>871</v>
+        <v>906</v>
       </c>
       <c r="K17" t="n">
-        <v>947</v>
+        <v>909</v>
       </c>
       <c r="L17" t="n">
-        <v>923.9</v>
+        <v>913.8</v>
       </c>
     </row>
     <row r="18">
@@ -1079,37 +1079,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>930</v>
+        <v>907</v>
       </c>
       <c r="C18" t="n">
-        <v>839</v>
+        <v>945</v>
       </c>
       <c r="D18" t="n">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="E18" t="n">
-        <v>823</v>
+        <v>836</v>
       </c>
       <c r="F18" t="n">
-        <v>830</v>
+        <v>880</v>
       </c>
       <c r="G18" t="n">
-        <v>912</v>
+        <v>944</v>
       </c>
       <c r="H18" t="n">
-        <v>875</v>
+        <v>817</v>
       </c>
       <c r="I18" t="n">
-        <v>1099</v>
+        <v>892</v>
       </c>
       <c r="J18" t="n">
-        <v>876</v>
+        <v>929</v>
       </c>
       <c r="K18" t="n">
-        <v>911</v>
+        <v>887</v>
       </c>
       <c r="L18" t="n">
-        <v>899.2</v>
+        <v>895.6</v>
       </c>
     </row>
     <row r="19">
@@ -1117,37 +1117,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>792</v>
+        <v>825</v>
       </c>
       <c r="C19" t="n">
-        <v>840</v>
+        <v>818</v>
       </c>
       <c r="D19" t="n">
-        <v>858</v>
+        <v>901</v>
       </c>
       <c r="E19" t="n">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="F19" t="n">
-        <v>858</v>
+        <v>903</v>
       </c>
       <c r="G19" t="n">
-        <v>761</v>
+        <v>863</v>
       </c>
       <c r="H19" t="n">
-        <v>834</v>
+        <v>816</v>
       </c>
       <c r="I19" t="n">
+        <v>793</v>
+      </c>
+      <c r="J19" t="n">
+        <v>841</v>
+      </c>
+      <c r="K19" t="n">
         <v>902</v>
       </c>
-      <c r="J19" t="n">
-        <v>1149</v>
-      </c>
-      <c r="K19" t="n">
-        <v>964</v>
-      </c>
       <c r="L19" t="n">
-        <v>876</v>
+        <v>846.1</v>
       </c>
     </row>
     <row r="20">
@@ -1155,37 +1155,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>786</v>
+        <v>1071</v>
       </c>
       <c r="C20" t="n">
-        <v>939</v>
+        <v>1092</v>
       </c>
       <c r="D20" t="n">
-        <v>924</v>
+        <v>895</v>
       </c>
       <c r="E20" t="n">
-        <v>938</v>
+        <v>889</v>
       </c>
       <c r="F20" t="n">
-        <v>891</v>
+        <v>931</v>
       </c>
       <c r="G20" t="n">
-        <v>917</v>
+        <v>828</v>
       </c>
       <c r="H20" t="n">
-        <v>1038</v>
+        <v>1174</v>
       </c>
       <c r="I20" t="n">
+        <v>928</v>
+      </c>
+      <c r="J20" t="n">
+        <v>956</v>
+      </c>
+      <c r="K20" t="n">
         <v>887</v>
       </c>
-      <c r="J20" t="n">
-        <v>874</v>
-      </c>
-      <c r="K20" t="n">
-        <v>882</v>
-      </c>
       <c r="L20" t="n">
-        <v>907.6</v>
+        <v>965.1</v>
       </c>
     </row>
     <row r="21">
@@ -1193,37 +1193,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>844</v>
+        <v>856</v>
       </c>
       <c r="C21" t="n">
-        <v>781</v>
+        <v>933</v>
       </c>
       <c r="D21" t="n">
-        <v>820</v>
+        <v>845</v>
       </c>
       <c r="E21" t="n">
-        <v>845</v>
+        <v>780</v>
       </c>
       <c r="F21" t="n">
-        <v>916</v>
+        <v>814</v>
       </c>
       <c r="G21" t="n">
-        <v>1121</v>
+        <v>930</v>
       </c>
       <c r="H21" t="n">
-        <v>818</v>
+        <v>805</v>
       </c>
       <c r="I21" t="n">
-        <v>814</v>
+        <v>775</v>
       </c>
       <c r="J21" t="n">
-        <v>929</v>
+        <v>917</v>
       </c>
       <c r="K21" t="n">
-        <v>943</v>
+        <v>930</v>
       </c>
       <c r="L21" t="n">
-        <v>883.1</v>
+        <v>858.5</v>
       </c>
     </row>
     <row r="22">
@@ -1231,37 +1231,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>840</v>
+        <v>848</v>
       </c>
       <c r="C22" t="n">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="D22" t="n">
         <v>839</v>
       </c>
       <c r="E22" t="n">
-        <v>908</v>
+        <v>864</v>
       </c>
       <c r="F22" t="n">
-        <v>922</v>
+        <v>848</v>
       </c>
       <c r="G22" t="n">
-        <v>849</v>
+        <v>810</v>
       </c>
       <c r="H22" t="n">
-        <v>765</v>
+        <v>868</v>
       </c>
       <c r="I22" t="n">
-        <v>855</v>
+        <v>974</v>
       </c>
       <c r="J22" t="n">
-        <v>890</v>
+        <v>883</v>
       </c>
       <c r="K22" t="n">
-        <v>774</v>
+        <v>914</v>
       </c>
       <c r="L22" t="n">
-        <v>843.9</v>
+        <v>864.7</v>
       </c>
     </row>
     <row r="23">
@@ -1269,37 +1269,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>927</v>
+        <v>890</v>
       </c>
       <c r="C23" t="n">
-        <v>979</v>
+        <v>1017</v>
       </c>
       <c r="D23" t="n">
-        <v>1090</v>
+        <v>1147</v>
       </c>
       <c r="E23" t="n">
-        <v>1004</v>
+        <v>1031</v>
       </c>
       <c r="F23" t="n">
-        <v>1024</v>
+        <v>972</v>
       </c>
       <c r="G23" t="n">
-        <v>1157</v>
+        <v>1053</v>
       </c>
       <c r="H23" t="n">
-        <v>974</v>
+        <v>894</v>
       </c>
       <c r="I23" t="n">
-        <v>1173</v>
+        <v>906</v>
       </c>
       <c r="J23" t="n">
-        <v>993</v>
+        <v>1068</v>
       </c>
       <c r="K23" t="n">
-        <v>975</v>
+        <v>1050</v>
       </c>
       <c r="L23" t="n">
-        <v>1029.6</v>
+        <v>1002.8</v>
       </c>
     </row>
     <row r="24">
@@ -1307,37 +1307,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>894</v>
+        <v>1041</v>
       </c>
       <c r="C24" t="n">
-        <v>883</v>
+        <v>848</v>
       </c>
       <c r="D24" t="n">
-        <v>1094</v>
+        <v>919</v>
       </c>
       <c r="E24" t="n">
-        <v>913</v>
+        <v>1036</v>
       </c>
       <c r="F24" t="n">
-        <v>1093</v>
+        <v>970</v>
       </c>
       <c r="G24" t="n">
-        <v>894</v>
+        <v>940</v>
       </c>
       <c r="H24" t="n">
-        <v>820</v>
+        <v>978</v>
       </c>
       <c r="I24" t="n">
-        <v>880</v>
+        <v>976</v>
       </c>
       <c r="J24" t="n">
-        <v>1004</v>
+        <v>828</v>
       </c>
       <c r="K24" t="n">
-        <v>854</v>
+        <v>977</v>
       </c>
       <c r="L24" t="n">
-        <v>932.9</v>
+        <v>951.3</v>
       </c>
     </row>
     <row r="25">
@@ -1345,37 +1345,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>883</v>
+        <v>935</v>
       </c>
       <c r="C25" t="n">
+        <v>904</v>
+      </c>
+      <c r="D25" t="n">
+        <v>828</v>
+      </c>
+      <c r="E25" t="n">
+        <v>922</v>
+      </c>
+      <c r="F25" t="n">
+        <v>875</v>
+      </c>
+      <c r="G25" t="n">
         <v>957</v>
       </c>
-      <c r="D25" t="n">
-        <v>913</v>
-      </c>
-      <c r="E25" t="n">
-        <v>1006</v>
-      </c>
-      <c r="F25" t="n">
-        <v>997</v>
-      </c>
-      <c r="G25" t="n">
-        <v>1081</v>
-      </c>
       <c r="H25" t="n">
-        <v>956</v>
+        <v>899</v>
       </c>
       <c r="I25" t="n">
-        <v>979</v>
+        <v>868</v>
       </c>
       <c r="J25" t="n">
-        <v>1063</v>
+        <v>1198</v>
       </c>
       <c r="K25" t="n">
-        <v>923</v>
+        <v>884</v>
       </c>
       <c r="L25" t="n">
-        <v>975.8</v>
+        <v>927</v>
       </c>
     </row>
     <row r="26">
@@ -1383,37 +1383,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>850</v>
+        <v>857</v>
       </c>
       <c r="C26" t="n">
-        <v>823</v>
+        <v>801</v>
       </c>
       <c r="D26" t="n">
-        <v>901</v>
+        <v>812</v>
       </c>
       <c r="E26" t="n">
-        <v>811</v>
+        <v>768</v>
       </c>
       <c r="F26" t="n">
-        <v>828</v>
+        <v>787</v>
       </c>
       <c r="G26" t="n">
-        <v>797</v>
+        <v>840</v>
       </c>
       <c r="H26" t="n">
-        <v>803</v>
+        <v>717</v>
       </c>
       <c r="I26" t="n">
-        <v>843</v>
+        <v>755</v>
       </c>
       <c r="J26" t="n">
-        <v>788</v>
+        <v>761</v>
       </c>
       <c r="K26" t="n">
-        <v>880</v>
+        <v>876</v>
       </c>
       <c r="L26" t="n">
-        <v>832.4</v>
+        <v>797.4</v>
       </c>
     </row>
     <row r="27">
@@ -1421,37 +1421,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>880</v>
+        <v>994</v>
       </c>
       <c r="C27" t="n">
-        <v>1083</v>
+        <v>825</v>
       </c>
       <c r="D27" t="n">
-        <v>1047</v>
+        <v>957</v>
       </c>
       <c r="E27" t="n">
-        <v>1112</v>
+        <v>1085</v>
       </c>
       <c r="F27" t="n">
-        <v>1020</v>
+        <v>941</v>
       </c>
       <c r="G27" t="n">
-        <v>883</v>
+        <v>1055</v>
       </c>
       <c r="H27" t="n">
-        <v>950</v>
+        <v>889</v>
       </c>
       <c r="I27" t="n">
-        <v>1103</v>
+        <v>1157</v>
       </c>
       <c r="J27" t="n">
-        <v>938</v>
+        <v>863</v>
       </c>
       <c r="K27" t="n">
-        <v>996</v>
+        <v>893</v>
       </c>
       <c r="L27" t="n">
-        <v>1001.2</v>
+        <v>965.9</v>
       </c>
     </row>
     <row r="28">
@@ -1459,37 +1459,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>898</v>
+        <v>978</v>
       </c>
       <c r="C28" t="n">
-        <v>1126</v>
+        <v>1017</v>
       </c>
       <c r="D28" t="n">
-        <v>968</v>
+        <v>1032</v>
       </c>
       <c r="E28" t="n">
-        <v>873</v>
+        <v>982</v>
       </c>
       <c r="F28" t="n">
-        <v>892</v>
+        <v>938</v>
       </c>
       <c r="G28" t="n">
-        <v>1065</v>
+        <v>964</v>
       </c>
       <c r="H28" t="n">
-        <v>1092</v>
+        <v>956</v>
       </c>
       <c r="I28" t="n">
-        <v>889</v>
+        <v>847</v>
       </c>
       <c r="J28" t="n">
-        <v>1005</v>
+        <v>939</v>
       </c>
       <c r="K28" t="n">
-        <v>937</v>
+        <v>940</v>
       </c>
       <c r="L28" t="n">
-        <v>974.5</v>
+        <v>959.3</v>
       </c>
     </row>
     <row r="29">
@@ -1497,37 +1497,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>853</v>
+        <v>948</v>
       </c>
       <c r="C29" t="n">
-        <v>974</v>
+        <v>798</v>
       </c>
       <c r="D29" t="n">
-        <v>791</v>
+        <v>852</v>
       </c>
       <c r="E29" t="n">
-        <v>947</v>
+        <v>838</v>
       </c>
       <c r="F29" t="n">
-        <v>979</v>
+        <v>833</v>
       </c>
       <c r="G29" t="n">
+        <v>770</v>
+      </c>
+      <c r="H29" t="n">
         <v>910</v>
       </c>
-      <c r="H29" t="n">
-        <v>838</v>
-      </c>
       <c r="I29" t="n">
-        <v>766</v>
+        <v>813</v>
       </c>
       <c r="J29" t="n">
-        <v>877</v>
+        <v>806</v>
       </c>
       <c r="K29" t="n">
-        <v>842</v>
+        <v>884</v>
       </c>
       <c r="L29" t="n">
-        <v>877.7</v>
+        <v>845.2</v>
       </c>
     </row>
     <row r="30">
@@ -1535,37 +1535,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>865</v>
+        <v>974</v>
       </c>
       <c r="C30" t="n">
-        <v>825</v>
+        <v>810</v>
       </c>
       <c r="D30" t="n">
-        <v>917</v>
+        <v>804</v>
       </c>
       <c r="E30" t="n">
-        <v>933</v>
+        <v>874</v>
       </c>
       <c r="F30" t="n">
-        <v>873</v>
+        <v>894</v>
       </c>
       <c r="G30" t="n">
-        <v>1030</v>
+        <v>989</v>
       </c>
       <c r="H30" t="n">
-        <v>876</v>
+        <v>869</v>
       </c>
       <c r="I30" t="n">
-        <v>1010</v>
+        <v>832</v>
       </c>
       <c r="J30" t="n">
-        <v>813</v>
+        <v>871</v>
       </c>
       <c r="K30" t="n">
-        <v>857</v>
+        <v>911</v>
       </c>
       <c r="L30" t="n">
-        <v>899.9</v>
+        <v>882.8</v>
       </c>
     </row>
     <row r="31">
@@ -1573,37 +1573,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>889</v>
+        <v>806</v>
       </c>
       <c r="C31" t="n">
-        <v>888</v>
+        <v>877</v>
       </c>
       <c r="D31" t="n">
-        <v>927</v>
+        <v>869</v>
       </c>
       <c r="E31" t="n">
-        <v>729</v>
+        <v>894</v>
       </c>
       <c r="F31" t="n">
-        <v>804</v>
+        <v>814</v>
       </c>
       <c r="G31" t="n">
-        <v>834</v>
+        <v>884</v>
       </c>
       <c r="H31" t="n">
-        <v>892</v>
+        <v>919</v>
       </c>
       <c r="I31" t="n">
-        <v>786</v>
+        <v>881</v>
       </c>
       <c r="J31" t="n">
-        <v>933</v>
+        <v>798</v>
       </c>
       <c r="K31" t="n">
-        <v>866</v>
+        <v>1101</v>
       </c>
       <c r="L31" t="n">
-        <v>854.8</v>
+        <v>884.3</v>
       </c>
     </row>
     <row r="32">
@@ -1611,37 +1611,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="C32" t="n">
-        <v>1013</v>
+        <v>983</v>
       </c>
       <c r="D32" t="n">
-        <v>787</v>
+        <v>863</v>
       </c>
       <c r="E32" t="n">
-        <v>1107</v>
+        <v>825</v>
       </c>
       <c r="F32" t="n">
-        <v>885</v>
+        <v>818</v>
       </c>
       <c r="G32" t="n">
-        <v>975</v>
+        <v>898</v>
       </c>
       <c r="H32" t="n">
-        <v>1185</v>
+        <v>843</v>
       </c>
       <c r="I32" t="n">
-        <v>1028</v>
+        <v>866</v>
       </c>
       <c r="J32" t="n">
-        <v>844</v>
+        <v>834</v>
       </c>
       <c r="K32" t="n">
-        <v>848</v>
+        <v>798</v>
       </c>
       <c r="L32" t="n">
-        <v>956.7</v>
+        <v>862.5</v>
       </c>
     </row>
     <row r="33">
@@ -1649,37 +1649,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>817</v>
+        <v>949</v>
       </c>
       <c r="C33" t="n">
-        <v>851</v>
+        <v>879</v>
       </c>
       <c r="D33" t="n">
-        <v>1015</v>
+        <v>804</v>
       </c>
       <c r="E33" t="n">
-        <v>817</v>
+        <v>795</v>
       </c>
       <c r="F33" t="n">
-        <v>959</v>
+        <v>886</v>
       </c>
       <c r="G33" t="n">
-        <v>906</v>
+        <v>883</v>
       </c>
       <c r="H33" t="n">
-        <v>785</v>
+        <v>876</v>
       </c>
       <c r="I33" t="n">
-        <v>912</v>
+        <v>1002</v>
       </c>
       <c r="J33" t="n">
-        <v>953</v>
+        <v>795</v>
       </c>
       <c r="K33" t="n">
-        <v>816</v>
+        <v>825</v>
       </c>
       <c r="L33" t="n">
-        <v>883.1</v>
+        <v>869.4</v>
       </c>
     </row>
     <row r="34">
@@ -1687,37 +1687,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>874</v>
+        <v>770</v>
       </c>
       <c r="C34" t="n">
-        <v>725</v>
+        <v>787</v>
       </c>
       <c r="D34" t="n">
-        <v>741</v>
+        <v>846</v>
       </c>
       <c r="E34" t="n">
-        <v>833</v>
+        <v>793</v>
       </c>
       <c r="F34" t="n">
-        <v>929</v>
+        <v>825</v>
       </c>
       <c r="G34" t="n">
-        <v>761</v>
+        <v>786</v>
       </c>
       <c r="H34" t="n">
-        <v>897</v>
+        <v>800</v>
       </c>
       <c r="I34" t="n">
-        <v>729</v>
+        <v>867</v>
       </c>
       <c r="J34" t="n">
-        <v>784</v>
+        <v>846</v>
       </c>
       <c r="K34" t="n">
-        <v>881</v>
+        <v>787</v>
       </c>
       <c r="L34" t="n">
-        <v>815.4</v>
+        <v>810.7</v>
       </c>
     </row>
     <row r="35">
@@ -1725,37 +1725,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>792</v>
+        <v>862</v>
       </c>
       <c r="C35" t="n">
-        <v>857</v>
+        <v>852</v>
       </c>
       <c r="D35" t="n">
+        <v>830</v>
+      </c>
+      <c r="E35" t="n">
+        <v>795</v>
+      </c>
+      <c r="F35" t="n">
+        <v>731</v>
+      </c>
+      <c r="G35" t="n">
+        <v>723</v>
+      </c>
+      <c r="H35" t="n">
+        <v>828</v>
+      </c>
+      <c r="I35" t="n">
+        <v>765</v>
+      </c>
+      <c r="J35" t="n">
+        <v>784</v>
+      </c>
+      <c r="K35" t="n">
         <v>863</v>
       </c>
-      <c r="E35" t="n">
-        <v>793</v>
-      </c>
-      <c r="F35" t="n">
-        <v>830</v>
-      </c>
-      <c r="G35" t="n">
-        <v>1012</v>
-      </c>
-      <c r="H35" t="n">
-        <v>800</v>
-      </c>
-      <c r="I35" t="n">
-        <v>686</v>
-      </c>
-      <c r="J35" t="n">
-        <v>793</v>
-      </c>
-      <c r="K35" t="n">
-        <v>866</v>
-      </c>
       <c r="L35" t="n">
-        <v>829.2</v>
+        <v>803.3</v>
       </c>
     </row>
     <row r="36">
@@ -1763,37 +1763,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>1018</v>
+        <v>974</v>
       </c>
       <c r="C36" t="n">
-        <v>956</v>
+        <v>1000</v>
       </c>
       <c r="D36" t="n">
-        <v>848</v>
+        <v>984</v>
       </c>
       <c r="E36" t="n">
-        <v>1116</v>
+        <v>981</v>
       </c>
       <c r="F36" t="n">
-        <v>984</v>
+        <v>960</v>
       </c>
       <c r="G36" t="n">
-        <v>1003</v>
+        <v>929</v>
       </c>
       <c r="H36" t="n">
-        <v>992</v>
+        <v>946</v>
       </c>
       <c r="I36" t="n">
-        <v>931</v>
+        <v>953</v>
       </c>
       <c r="J36" t="n">
-        <v>884</v>
+        <v>939</v>
       </c>
       <c r="K36" t="n">
-        <v>902</v>
+        <v>936</v>
       </c>
       <c r="L36" t="n">
-        <v>963.4</v>
+        <v>960.2</v>
       </c>
     </row>
     <row r="37">
@@ -1801,37 +1801,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>928</v>
+        <v>870</v>
       </c>
       <c r="C37" t="n">
-        <v>923</v>
+        <v>817</v>
       </c>
       <c r="D37" t="n">
-        <v>798</v>
+        <v>809</v>
       </c>
       <c r="E37" t="n">
-        <v>906</v>
+        <v>1035</v>
       </c>
       <c r="F37" t="n">
-        <v>695</v>
+        <v>852</v>
       </c>
       <c r="G37" t="n">
+        <v>808</v>
+      </c>
+      <c r="H37" t="n">
+        <v>858</v>
+      </c>
+      <c r="I37" t="n">
+        <v>808</v>
+      </c>
+      <c r="J37" t="n">
+        <v>889</v>
+      </c>
+      <c r="K37" t="n">
         <v>754</v>
       </c>
-      <c r="H37" t="n">
-        <v>978</v>
-      </c>
-      <c r="I37" t="n">
-        <v>746</v>
-      </c>
-      <c r="J37" t="n">
-        <v>861</v>
-      </c>
-      <c r="K37" t="n">
-        <v>790</v>
-      </c>
       <c r="L37" t="n">
-        <v>837.9</v>
+        <v>850</v>
       </c>
     </row>
     <row r="38">
@@ -1839,37 +1839,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>770</v>
+        <v>847</v>
       </c>
       <c r="C38" t="n">
-        <v>843</v>
+        <v>828</v>
       </c>
       <c r="D38" t="n">
-        <v>875</v>
+        <v>901</v>
       </c>
       <c r="E38" t="n">
-        <v>912</v>
+        <v>825</v>
       </c>
       <c r="F38" t="n">
-        <v>917</v>
+        <v>914</v>
       </c>
       <c r="G38" t="n">
-        <v>844</v>
+        <v>802</v>
       </c>
       <c r="H38" t="n">
-        <v>825</v>
+        <v>930</v>
       </c>
       <c r="I38" t="n">
-        <v>826</v>
+        <v>872</v>
       </c>
       <c r="J38" t="n">
-        <v>833</v>
+        <v>870</v>
       </c>
       <c r="K38" t="n">
-        <v>930</v>
+        <v>907</v>
       </c>
       <c r="L38" t="n">
-        <v>857.5</v>
+        <v>869.6</v>
       </c>
     </row>
     <row r="39">
@@ -1877,37 +1877,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>783</v>
+        <v>926</v>
       </c>
       <c r="C39" t="n">
-        <v>858</v>
+        <v>839</v>
       </c>
       <c r="D39" t="n">
-        <v>719</v>
+        <v>919</v>
       </c>
       <c r="E39" t="n">
-        <v>800</v>
+        <v>777</v>
       </c>
       <c r="F39" t="n">
-        <v>670</v>
+        <v>925</v>
       </c>
       <c r="G39" t="n">
-        <v>873</v>
+        <v>868</v>
       </c>
       <c r="H39" t="n">
-        <v>935</v>
+        <v>919</v>
       </c>
       <c r="I39" t="n">
-        <v>832</v>
+        <v>820</v>
       </c>
       <c r="J39" t="n">
-        <v>861</v>
+        <v>866</v>
       </c>
       <c r="K39" t="n">
-        <v>783</v>
+        <v>895</v>
       </c>
       <c r="L39" t="n">
-        <v>811.4</v>
+        <v>875.4</v>
       </c>
     </row>
     <row r="40">
@@ -1915,37 +1915,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>753</v>
+        <v>1090</v>
       </c>
       <c r="C40" t="n">
-        <v>852</v>
+        <v>888</v>
       </c>
       <c r="D40" t="n">
-        <v>828</v>
+        <v>938</v>
       </c>
       <c r="E40" t="n">
-        <v>819</v>
+        <v>862</v>
       </c>
       <c r="F40" t="n">
-        <v>1016</v>
+        <v>1095</v>
       </c>
       <c r="G40" t="n">
-        <v>805</v>
+        <v>953</v>
       </c>
       <c r="H40" t="n">
-        <v>795</v>
+        <v>913</v>
       </c>
       <c r="I40" t="n">
-        <v>896</v>
+        <v>938</v>
       </c>
       <c r="J40" t="n">
-        <v>919</v>
+        <v>811</v>
       </c>
       <c r="K40" t="n">
-        <v>893</v>
+        <v>840</v>
       </c>
       <c r="L40" t="n">
-        <v>857.6</v>
+        <v>932.8</v>
       </c>
     </row>
     <row r="41">
@@ -1953,37 +1953,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>758</v>
+        <v>836</v>
       </c>
       <c r="C41" t="n">
-        <v>840</v>
+        <v>893</v>
       </c>
       <c r="D41" t="n">
-        <v>979</v>
+        <v>1084</v>
       </c>
       <c r="E41" t="n">
-        <v>981</v>
+        <v>967</v>
       </c>
       <c r="F41" t="n">
+        <v>1052</v>
+      </c>
+      <c r="G41" t="n">
+        <v>842</v>
+      </c>
+      <c r="H41" t="n">
         <v>838</v>
       </c>
-      <c r="G41" t="n">
-        <v>851</v>
-      </c>
-      <c r="H41" t="n">
-        <v>862</v>
-      </c>
       <c r="I41" t="n">
-        <v>812</v>
+        <v>1073</v>
       </c>
       <c r="J41" t="n">
-        <v>939</v>
+        <v>1006</v>
       </c>
       <c r="K41" t="n">
-        <v>913</v>
+        <v>800</v>
       </c>
       <c r="L41" t="n">
-        <v>877.3</v>
+        <v>939.1</v>
       </c>
     </row>
     <row r="42">
@@ -1991,37 +1991,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>888</v>
+        <v>868</v>
       </c>
       <c r="C42" t="n">
-        <v>848</v>
+        <v>817</v>
       </c>
       <c r="D42" t="n">
-        <v>806</v>
+        <v>909</v>
       </c>
       <c r="E42" t="n">
-        <v>782</v>
+        <v>901</v>
       </c>
       <c r="F42" t="n">
-        <v>732</v>
+        <v>750</v>
       </c>
       <c r="G42" t="n">
-        <v>856</v>
+        <v>800</v>
       </c>
       <c r="H42" t="n">
-        <v>741</v>
+        <v>869</v>
       </c>
       <c r="I42" t="n">
-        <v>844</v>
+        <v>804</v>
       </c>
       <c r="J42" t="n">
-        <v>687</v>
+        <v>772</v>
       </c>
       <c r="K42" t="n">
-        <v>808</v>
+        <v>731</v>
       </c>
       <c r="L42" t="n">
-        <v>799.2</v>
+        <v>822.1</v>
       </c>
     </row>
     <row r="43">
@@ -2029,37 +2029,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>785</v>
+        <v>889</v>
       </c>
       <c r="C43" t="n">
-        <v>881</v>
+        <v>795</v>
       </c>
       <c r="D43" t="n">
-        <v>872</v>
+        <v>960</v>
       </c>
       <c r="E43" t="n">
-        <v>818</v>
+        <v>952</v>
       </c>
       <c r="F43" t="n">
-        <v>807</v>
+        <v>772</v>
       </c>
       <c r="G43" t="n">
-        <v>879</v>
+        <v>817</v>
       </c>
       <c r="H43" t="n">
-        <v>806</v>
+        <v>871</v>
       </c>
       <c r="I43" t="n">
-        <v>777</v>
+        <v>987</v>
       </c>
       <c r="J43" t="n">
-        <v>892</v>
+        <v>829</v>
       </c>
       <c r="K43" t="n">
-        <v>913</v>
+        <v>859</v>
       </c>
       <c r="L43" t="n">
-        <v>843</v>
+        <v>873.1</v>
       </c>
     </row>
     <row r="44">
@@ -2067,37 +2067,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>815</v>
+        <v>867</v>
       </c>
       <c r="C44" t="n">
-        <v>805</v>
+        <v>849</v>
       </c>
       <c r="D44" t="n">
-        <v>752</v>
+        <v>874</v>
       </c>
       <c r="E44" t="n">
-        <v>837</v>
+        <v>1005</v>
       </c>
       <c r="F44" t="n">
-        <v>823</v>
+        <v>817</v>
       </c>
       <c r="G44" t="n">
-        <v>797</v>
+        <v>831</v>
       </c>
       <c r="H44" t="n">
-        <v>848</v>
+        <v>917</v>
       </c>
       <c r="I44" t="n">
-        <v>1054</v>
+        <v>858</v>
       </c>
       <c r="J44" t="n">
         <v>798</v>
       </c>
       <c r="K44" t="n">
-        <v>795</v>
+        <v>813</v>
       </c>
       <c r="L44" t="n">
-        <v>832.4</v>
+        <v>862.9</v>
       </c>
     </row>
     <row r="45">
@@ -2105,37 +2105,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>1044</v>
+        <v>890</v>
       </c>
       <c r="C45" t="n">
-        <v>754</v>
+        <v>792</v>
       </c>
       <c r="D45" t="n">
-        <v>960</v>
+        <v>865</v>
       </c>
       <c r="E45" t="n">
-        <v>873</v>
+        <v>979</v>
       </c>
       <c r="F45" t="n">
-        <v>1067</v>
+        <v>926</v>
       </c>
       <c r="G45" t="n">
-        <v>858</v>
+        <v>849</v>
       </c>
       <c r="H45" t="n">
-        <v>836</v>
+        <v>891</v>
       </c>
       <c r="I45" t="n">
-        <v>893</v>
+        <v>1034</v>
       </c>
       <c r="J45" t="n">
-        <v>898</v>
+        <v>935</v>
       </c>
       <c r="K45" t="n">
-        <v>839</v>
+        <v>961</v>
       </c>
       <c r="L45" t="n">
-        <v>902.2</v>
+        <v>912.2</v>
       </c>
     </row>
     <row r="46">
@@ -2143,37 +2143,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>809</v>
+        <v>896</v>
       </c>
       <c r="C46" t="n">
-        <v>866</v>
+        <v>850</v>
       </c>
       <c r="D46" t="n">
-        <v>816</v>
+        <v>930</v>
       </c>
       <c r="E46" t="n">
-        <v>812</v>
+        <v>850</v>
       </c>
       <c r="F46" t="n">
-        <v>874</v>
+        <v>954</v>
       </c>
       <c r="G46" t="n">
-        <v>907</v>
+        <v>831</v>
       </c>
       <c r="H46" t="n">
-        <v>747</v>
+        <v>936</v>
       </c>
       <c r="I46" t="n">
-        <v>934</v>
+        <v>937</v>
       </c>
       <c r="J46" t="n">
-        <v>936</v>
+        <v>893</v>
       </c>
       <c r="K46" t="n">
-        <v>832</v>
+        <v>850</v>
       </c>
       <c r="L46" t="n">
-        <v>853.3</v>
+        <v>892.7</v>
       </c>
     </row>
     <row r="47">
@@ -2181,37 +2181,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>958</v>
+        <v>1094</v>
       </c>
       <c r="C47" t="n">
-        <v>888</v>
+        <v>1024</v>
       </c>
       <c r="D47" t="n">
-        <v>908</v>
+        <v>1072</v>
       </c>
       <c r="E47" t="n">
-        <v>987</v>
+        <v>926</v>
       </c>
       <c r="F47" t="n">
-        <v>998</v>
+        <v>1126</v>
       </c>
       <c r="G47" t="n">
-        <v>1028</v>
+        <v>1007</v>
       </c>
       <c r="H47" t="n">
-        <v>887</v>
+        <v>923</v>
       </c>
       <c r="I47" t="n">
-        <v>880</v>
+        <v>905</v>
       </c>
       <c r="J47" t="n">
-        <v>912</v>
+        <v>950</v>
       </c>
       <c r="K47" t="n">
-        <v>923</v>
+        <v>1030</v>
       </c>
       <c r="L47" t="n">
-        <v>936.9</v>
+        <v>1005.7</v>
       </c>
     </row>
     <row r="48">
@@ -2219,37 +2219,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>858</v>
+        <v>828</v>
       </c>
       <c r="C48" t="n">
-        <v>893</v>
+        <v>792</v>
       </c>
       <c r="D48" t="n">
-        <v>838</v>
+        <v>889</v>
       </c>
       <c r="E48" t="n">
-        <v>752</v>
+        <v>870</v>
       </c>
       <c r="F48" t="n">
-        <v>855</v>
+        <v>876</v>
       </c>
       <c r="G48" t="n">
         <v>842</v>
       </c>
       <c r="H48" t="n">
-        <v>815</v>
+        <v>745</v>
       </c>
       <c r="I48" t="n">
-        <v>1036</v>
+        <v>819</v>
       </c>
       <c r="J48" t="n">
-        <v>944</v>
+        <v>814</v>
       </c>
       <c r="K48" t="n">
-        <v>835</v>
+        <v>892</v>
       </c>
       <c r="L48" t="n">
-        <v>866.8</v>
+        <v>836.7</v>
       </c>
     </row>
     <row r="49">
@@ -2257,37 +2257,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>967</v>
+        <v>869</v>
       </c>
       <c r="C49" t="n">
-        <v>1023</v>
+        <v>1013</v>
       </c>
       <c r="D49" t="n">
-        <v>975</v>
+        <v>805</v>
       </c>
       <c r="E49" t="n">
-        <v>941</v>
+        <v>885</v>
       </c>
       <c r="F49" t="n">
-        <v>901</v>
+        <v>980</v>
       </c>
       <c r="G49" t="n">
+        <v>837</v>
+      </c>
+      <c r="H49" t="n">
+        <v>900</v>
+      </c>
+      <c r="I49" t="n">
         <v>831</v>
       </c>
-      <c r="H49" t="n">
-        <v>875</v>
-      </c>
-      <c r="I49" t="n">
-        <v>852</v>
-      </c>
       <c r="J49" t="n">
-        <v>863</v>
+        <v>844</v>
       </c>
       <c r="K49" t="n">
-        <v>1072</v>
+        <v>932</v>
       </c>
       <c r="L49" t="n">
-        <v>930</v>
+        <v>889.6</v>
       </c>
     </row>
     <row r="50">
@@ -2295,37 +2295,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>796</v>
+        <v>906</v>
       </c>
       <c r="C50" t="n">
-        <v>939</v>
+        <v>800</v>
       </c>
       <c r="D50" t="n">
-        <v>863</v>
+        <v>818</v>
       </c>
       <c r="E50" t="n">
+        <v>913</v>
+      </c>
+      <c r="F50" t="n">
+        <v>877</v>
+      </c>
+      <c r="G50" t="n">
+        <v>903</v>
+      </c>
+      <c r="H50" t="n">
         <v>928</v>
       </c>
-      <c r="F50" t="n">
-        <v>943</v>
-      </c>
-      <c r="G50" t="n">
+      <c r="I50" t="n">
+        <v>948</v>
+      </c>
+      <c r="J50" t="n">
         <v>842</v>
       </c>
-      <c r="H50" t="n">
-        <v>870</v>
-      </c>
-      <c r="I50" t="n">
-        <v>985</v>
-      </c>
-      <c r="J50" t="n">
-        <v>944</v>
-      </c>
       <c r="K50" t="n">
-        <v>941</v>
+        <v>831</v>
       </c>
       <c r="L50" t="n">
-        <v>905.1</v>
+        <v>876.6</v>
       </c>
     </row>
     <row r="51">
@@ -2333,37 +2333,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>901</v>
+        <v>950</v>
       </c>
       <c r="C51" t="n">
-        <v>938</v>
+        <v>888</v>
       </c>
       <c r="D51" t="n">
-        <v>859</v>
+        <v>881</v>
       </c>
       <c r="E51" t="n">
-        <v>1009</v>
+        <v>945</v>
       </c>
       <c r="F51" t="n">
-        <v>922</v>
+        <v>828</v>
       </c>
       <c r="G51" t="n">
-        <v>836</v>
+        <v>862</v>
       </c>
       <c r="H51" t="n">
-        <v>917</v>
+        <v>889</v>
       </c>
       <c r="I51" t="n">
-        <v>843</v>
+        <v>876</v>
       </c>
       <c r="J51" t="n">
-        <v>870</v>
+        <v>819</v>
       </c>
       <c r="K51" t="n">
-        <v>841</v>
+        <v>954</v>
       </c>
       <c r="L51" t="n">
-        <v>893.6</v>
+        <v>889.2</v>
       </c>
     </row>
     <row r="52">
@@ -2373,37 +2373,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>859.78</v>
+        <v>898.92</v>
       </c>
       <c r="C52" t="n">
-        <v>879.9</v>
+        <v>869.62</v>
       </c>
       <c r="D52" t="n">
-        <v>877.14</v>
+        <v>891.26</v>
       </c>
       <c r="E52" t="n">
-        <v>885.16</v>
+        <v>892.74</v>
       </c>
       <c r="F52" t="n">
-        <v>886.86</v>
+        <v>876.08</v>
       </c>
       <c r="G52" t="n">
-        <v>889.96</v>
+        <v>877.5</v>
       </c>
       <c r="H52" t="n">
-        <v>876.2</v>
+        <v>872.58</v>
       </c>
       <c r="I52" t="n">
-        <v>890.1799999999999</v>
+        <v>887.62</v>
       </c>
       <c r="J52" t="n">
-        <v>885.6</v>
+        <v>877.7</v>
       </c>
       <c r="K52" t="n">
-        <v>884.4400000000001</v>
+        <v>878.96</v>
       </c>
       <c r="L52" t="n">
-        <v>881.5219999999998</v>
+        <v>882.298</v>
       </c>
     </row>
   </sheetData>
@@ -2462,37 +2462,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>6.480181932449341</v>
+        <v>8.600137948989868</v>
       </c>
       <c r="C2" t="n">
-        <v>6.559860467910767</v>
+        <v>6.695988416671753</v>
       </c>
       <c r="D2" t="n">
-        <v>9.630515336990356</v>
+        <v>6.303443908691406</v>
       </c>
       <c r="E2" t="n">
-        <v>7.040117740631104</v>
+        <v>6.71246600151062</v>
       </c>
       <c r="F2" t="n">
-        <v>8.68943977355957</v>
+        <v>6.567260980606079</v>
       </c>
       <c r="G2" t="n">
-        <v>7.538355588912964</v>
+        <v>6.412676095962524</v>
       </c>
       <c r="H2" t="n">
-        <v>6.914937734603882</v>
+        <v>6.844598293304443</v>
       </c>
       <c r="I2" t="n">
-        <v>7.058122396469116</v>
+        <v>6.131897926330566</v>
       </c>
       <c r="J2" t="n">
-        <v>6.82227635383606</v>
+        <v>6.719400644302368</v>
       </c>
       <c r="K2" t="n">
-        <v>6.335071325302124</v>
+        <v>6.490002155303955</v>
       </c>
       <c r="L2" t="n">
-        <v>7.306887865066528</v>
+        <v>6.747787237167358</v>
       </c>
     </row>
     <row r="3">
@@ -2500,37 +2500,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>6.523595333099365</v>
+        <v>6.883989572525024</v>
       </c>
       <c r="C3" t="n">
-        <v>7.118049383163452</v>
+        <v>6.975736618041992</v>
       </c>
       <c r="D3" t="n">
-        <v>7.044687986373901</v>
+        <v>6.36779522895813</v>
       </c>
       <c r="E3" t="n">
-        <v>6.51427698135376</v>
+        <v>7.079484462738037</v>
       </c>
       <c r="F3" t="n">
-        <v>7.234615087509155</v>
+        <v>6.820641040802002</v>
       </c>
       <c r="G3" t="n">
-        <v>7.210659027099609</v>
+        <v>6.420667886734009</v>
       </c>
       <c r="H3" t="n">
-        <v>6.835178852081299</v>
+        <v>6.618722200393677</v>
       </c>
       <c r="I3" t="n">
-        <v>7.692430019378662</v>
+        <v>7.623248815536499</v>
       </c>
       <c r="J3" t="n">
-        <v>6.530898094177246</v>
+        <v>6.251740694046021</v>
       </c>
       <c r="K3" t="n">
-        <v>8.554301500320435</v>
+        <v>6.634739875793457</v>
       </c>
       <c r="L3" t="n">
-        <v>7.125869226455689</v>
+        <v>6.767676639556885</v>
       </c>
     </row>
     <row r="4">
@@ -2538,37 +2538,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>7.41409969329834</v>
+        <v>6.431292533874512</v>
       </c>
       <c r="C4" t="n">
-        <v>6.662098169326782</v>
+        <v>6.529052257537842</v>
       </c>
       <c r="D4" t="n">
-        <v>8.811581134796143</v>
+        <v>6.563263177871704</v>
       </c>
       <c r="E4" t="n">
-        <v>6.959424018859863</v>
+        <v>6.721354722976685</v>
       </c>
       <c r="F4" t="n">
-        <v>6.430163383483887</v>
+        <v>7.342422485351562</v>
       </c>
       <c r="G4" t="n">
-        <v>6.856550455093384</v>
+        <v>7.133465766906738</v>
       </c>
       <c r="H4" t="n">
-        <v>6.773785352706909</v>
+        <v>6.736018180847168</v>
       </c>
       <c r="I4" t="n">
-        <v>6.43568754196167</v>
+        <v>8.132323980331421</v>
       </c>
       <c r="J4" t="n">
-        <v>6.750320911407471</v>
+        <v>6.677148818969727</v>
       </c>
       <c r="K4" t="n">
-        <v>7.997490167617798</v>
+        <v>7.571873426437378</v>
       </c>
       <c r="L4" t="n">
-        <v>7.109120082855225</v>
+        <v>6.983821535110474</v>
       </c>
     </row>
     <row r="5">
@@ -2576,37 +2576,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>9.013604640960693</v>
+        <v>5.83686351776123</v>
       </c>
       <c r="C5" t="n">
-        <v>6.389638423919678</v>
+        <v>5.76202130317688</v>
       </c>
       <c r="D5" t="n">
-        <v>6.319446325302124</v>
+        <v>5.803899049758911</v>
       </c>
       <c r="E5" t="n">
-        <v>6.120653390884399</v>
+        <v>6.06323504447937</v>
       </c>
       <c r="F5" t="n">
-        <v>6.535859346389771</v>
+        <v>5.993515014648438</v>
       </c>
       <c r="G5" t="n">
-        <v>6.315441131591797</v>
+        <v>5.843812227249146</v>
       </c>
       <c r="H5" t="n">
-        <v>8.324345588684082</v>
+        <v>6.145050287246704</v>
       </c>
       <c r="I5" t="n">
-        <v>6.112927198410034</v>
+        <v>5.874744892120361</v>
       </c>
       <c r="J5" t="n">
-        <v>5.858692169189453</v>
+        <v>5.747073650360107</v>
       </c>
       <c r="K5" t="n">
-        <v>6.982365369796753</v>
+        <v>6.057295322418213</v>
       </c>
       <c r="L5" t="n">
-        <v>6.797297358512878</v>
+        <v>5.912751030921936</v>
       </c>
     </row>
     <row r="6">
@@ -2614,37 +2614,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>5.86624550819397</v>
+        <v>5.571572065353394</v>
       </c>
       <c r="C6" t="n">
-        <v>5.671399354934692</v>
+        <v>5.439863443374634</v>
       </c>
       <c r="D6" t="n">
-        <v>5.675042629241943</v>
+        <v>5.26082706451416</v>
       </c>
       <c r="E6" t="n">
-        <v>5.86461615562439</v>
+        <v>5.245649337768555</v>
       </c>
       <c r="F6" t="n">
-        <v>6.150877714157104</v>
+        <v>5.926476240158081</v>
       </c>
       <c r="G6" t="n">
-        <v>6.014705896377563</v>
+        <v>6.125933647155762</v>
       </c>
       <c r="H6" t="n">
-        <v>5.709981203079224</v>
+        <v>5.553861141204834</v>
       </c>
       <c r="I6" t="n">
-        <v>5.803277254104614</v>
+        <v>5.517465114593506</v>
       </c>
       <c r="J6" t="n">
-        <v>5.720001459121704</v>
+        <v>5.548137187957764</v>
       </c>
       <c r="K6" t="n">
-        <v>6.186262130737305</v>
+        <v>5.533129930496216</v>
       </c>
       <c r="L6" t="n">
-        <v>5.866240930557251</v>
+        <v>5.572291517257691</v>
       </c>
     </row>
     <row r="7">
@@ -2652,37 +2652,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>7.583226203918457</v>
+        <v>7.079155921936035</v>
       </c>
       <c r="C7" t="n">
-        <v>9.15871787071228</v>
+        <v>7.203267097473145</v>
       </c>
       <c r="D7" t="n">
-        <v>7.417133092880249</v>
+        <v>7.177820920944214</v>
       </c>
       <c r="E7" t="n">
-        <v>8.103885412216187</v>
+        <v>7.440211534500122</v>
       </c>
       <c r="F7" t="n">
-        <v>9.548349857330322</v>
+        <v>7.542417287826538</v>
       </c>
       <c r="G7" t="n">
-        <v>7.689937114715576</v>
+        <v>8.000629425048828</v>
       </c>
       <c r="H7" t="n">
-        <v>7.443055152893066</v>
+        <v>6.811669588088989</v>
       </c>
       <c r="I7" t="n">
-        <v>8.293432235717773</v>
+        <v>7.262490034103394</v>
       </c>
       <c r="J7" t="n">
-        <v>7.208660840988159</v>
+        <v>8.111851692199707</v>
       </c>
       <c r="K7" t="n">
-        <v>7.020146369934082</v>
+        <v>6.721416234970093</v>
       </c>
       <c r="L7" t="n">
-        <v>7.946654415130615</v>
+        <v>7.335092973709107</v>
       </c>
     </row>
     <row r="8">
@@ -2690,37 +2690,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>7.756787538528442</v>
+        <v>7.618993282318115</v>
       </c>
       <c r="C8" t="n">
-        <v>7.191740036010742</v>
+        <v>7.559373378753662</v>
       </c>
       <c r="D8" t="n">
-        <v>6.801685094833374</v>
+        <v>7.142940044403076</v>
       </c>
       <c r="E8" t="n">
-        <v>6.64745831489563</v>
+        <v>7.455634832382202</v>
       </c>
       <c r="F8" t="n">
-        <v>7.321509122848511</v>
+        <v>6.842714309692383</v>
       </c>
       <c r="G8" t="n">
-        <v>7.399795770645142</v>
+        <v>7.314510345458984</v>
       </c>
       <c r="H8" t="n">
-        <v>7.011771202087402</v>
+        <v>7.206263303756714</v>
       </c>
       <c r="I8" t="n">
-        <v>9.158717393875122</v>
+        <v>7.150953054428101</v>
       </c>
       <c r="J8" t="n">
-        <v>7.700536012649536</v>
+        <v>6.942472219467163</v>
       </c>
       <c r="K8" t="n">
-        <v>7.126970767974854</v>
+        <v>7.199283838272095</v>
       </c>
       <c r="L8" t="n">
-        <v>7.411697125434875</v>
+        <v>7.24331386089325</v>
       </c>
     </row>
     <row r="9">
@@ -2728,37 +2728,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>7.10908055305481</v>
+        <v>7.708535194396973</v>
       </c>
       <c r="C9" t="n">
-        <v>7.358890295028687</v>
+        <v>7.068859577178955</v>
       </c>
       <c r="D9" t="n">
-        <v>6.52854323387146</v>
+        <v>6.563796997070312</v>
       </c>
       <c r="E9" t="n">
-        <v>7.241262674331665</v>
+        <v>6.89595103263855</v>
       </c>
       <c r="F9" t="n">
-        <v>8.567051410675049</v>
+        <v>7.690943717956543</v>
       </c>
       <c r="G9" t="n">
-        <v>6.736618757247925</v>
+        <v>7.620587348937988</v>
       </c>
       <c r="H9" t="n">
-        <v>6.899624824523926</v>
+        <v>7.558228969573975</v>
       </c>
       <c r="I9" t="n">
-        <v>6.975408792495728</v>
+        <v>8.420543909072876</v>
       </c>
       <c r="J9" t="n">
-        <v>7.192289113998413</v>
+        <v>8.879889488220215</v>
       </c>
       <c r="K9" t="n">
-        <v>7.213265895843506</v>
+        <v>7.151318311691284</v>
       </c>
       <c r="L9" t="n">
-        <v>7.182203555107117</v>
+        <v>7.555865454673767</v>
       </c>
     </row>
     <row r="10">
@@ -2766,37 +2766,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>6.370477676391602</v>
+        <v>7.39715576171875</v>
       </c>
       <c r="C10" t="n">
-        <v>6.197883129119873</v>
+        <v>6.122904300689697</v>
       </c>
       <c r="D10" t="n">
-        <v>6.698383331298828</v>
+        <v>6.151850938796997</v>
       </c>
       <c r="E10" t="n">
-        <v>6.161319255828857</v>
+        <v>8.74674916267395</v>
       </c>
       <c r="F10" t="n">
-        <v>5.664638519287109</v>
+        <v>6.113970756530762</v>
       </c>
       <c r="G10" t="n">
-        <v>6.464207649230957</v>
+        <v>6.604201316833496</v>
       </c>
       <c r="H10" t="n">
-        <v>6.275529623031616</v>
+        <v>6.077537775039673</v>
       </c>
       <c r="I10" t="n">
-        <v>7.028133869171143</v>
+        <v>6.571300268173218</v>
       </c>
       <c r="J10" t="n">
-        <v>6.423661947250366</v>
+        <v>6.036621570587158</v>
       </c>
       <c r="K10" t="n">
-        <v>9.016068935394287</v>
+        <v>5.993759870529175</v>
       </c>
       <c r="L10" t="n">
-        <v>6.630030393600464</v>
+        <v>6.581605172157287</v>
       </c>
     </row>
     <row r="11">
@@ -2804,37 +2804,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>7.103432893753052</v>
+        <v>6.618177890777588</v>
       </c>
       <c r="C11" t="n">
-        <v>7.217653512954712</v>
+        <v>6.696346998214722</v>
       </c>
       <c r="D11" t="n">
-        <v>6.788225173950195</v>
+        <v>6.279688596725464</v>
       </c>
       <c r="E11" t="n">
-        <v>6.641617298126221</v>
+        <v>6.405845642089844</v>
       </c>
       <c r="F11" t="n">
-        <v>6.578536748886108</v>
+        <v>6.434791326522827</v>
       </c>
       <c r="G11" t="n">
-        <v>6.641618490219116</v>
+        <v>6.754969596862793</v>
       </c>
       <c r="H11" t="n">
-        <v>6.493485450744629</v>
+        <v>8.072563171386719</v>
       </c>
       <c r="I11" t="n">
-        <v>6.693494081497192</v>
+        <v>6.408348560333252</v>
       </c>
       <c r="J11" t="n">
-        <v>8.077941656112671</v>
+        <v>6.732022047042847</v>
       </c>
       <c r="K11" t="n">
-        <v>7.029126644134521</v>
+        <v>7.200297117233276</v>
       </c>
       <c r="L11" t="n">
-        <v>6.926513195037842</v>
+        <v>6.760305094718933</v>
       </c>
     </row>
     <row r="12">
@@ -2842,37 +2842,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>7.720872402191162</v>
+        <v>6.691638231277466</v>
       </c>
       <c r="C12" t="n">
-        <v>9.714958190917969</v>
+        <v>9.655461549758911</v>
       </c>
       <c r="D12" t="n">
-        <v>7.274986505508423</v>
+        <v>6.999839067459106</v>
       </c>
       <c r="E12" t="n">
-        <v>7.413133382797241</v>
+        <v>7.129925012588501</v>
       </c>
       <c r="F12" t="n">
-        <v>7.272502183914185</v>
+        <v>6.836260557174683</v>
       </c>
       <c r="G12" t="n">
-        <v>6.756843328475952</v>
+        <v>7.223235130310059</v>
       </c>
       <c r="H12" t="n">
-        <v>7.553264379501343</v>
+        <v>6.655707359313965</v>
       </c>
       <c r="I12" t="n">
-        <v>7.689988613128662</v>
+        <v>6.64529275894165</v>
       </c>
       <c r="J12" t="n">
-        <v>8.360247850418091</v>
+        <v>6.858185768127441</v>
       </c>
       <c r="K12" t="n">
-        <v>6.953801393508911</v>
+        <v>6.920533657073975</v>
       </c>
       <c r="L12" t="n">
-        <v>7.671059823036193</v>
+        <v>7.161607909202576</v>
       </c>
     </row>
     <row r="13">
@@ -2880,37 +2880,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>5.790754556655884</v>
+        <v>6.306123971939087</v>
       </c>
       <c r="C13" t="n">
-        <v>6.386791944503784</v>
+        <v>6.113667964935303</v>
       </c>
       <c r="D13" t="n">
-        <v>6.31541919708252</v>
+        <v>6.089673280715942</v>
       </c>
       <c r="E13" t="n">
-        <v>6.961289644241333</v>
+        <v>6.67716121673584</v>
       </c>
       <c r="F13" t="n">
-        <v>6.209723711013794</v>
+        <v>6.104635238647461</v>
       </c>
       <c r="G13" t="n">
-        <v>6.427482843399048</v>
+        <v>6.431280612945557</v>
       </c>
       <c r="H13" t="n">
-        <v>6.50211501121521</v>
+        <v>7.179718494415283</v>
       </c>
       <c r="I13" t="n">
-        <v>6.083711385726929</v>
+        <v>6.326440095901489</v>
       </c>
       <c r="J13" t="n">
-        <v>7.643187999725342</v>
+        <v>6.676549673080444</v>
       </c>
       <c r="K13" t="n">
-        <v>6.500621557235718</v>
+        <v>6.395443439483643</v>
       </c>
       <c r="L13" t="n">
-        <v>6.482109785079956</v>
+        <v>6.430069398880005</v>
       </c>
     </row>
     <row r="14">
@@ -2918,37 +2918,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>7.199369668960571</v>
+        <v>9.469012498855591</v>
       </c>
       <c r="C14" t="n">
-        <v>8.715890884399414</v>
+        <v>7.437648773193359</v>
       </c>
       <c r="D14" t="n">
-        <v>7.310529470443726</v>
+        <v>7.154355049133301</v>
       </c>
       <c r="E14" t="n">
-        <v>7.027269601821899</v>
+        <v>7.292032241821289</v>
       </c>
       <c r="F14" t="n">
-        <v>7.429135799407959</v>
+        <v>6.85158634185791</v>
       </c>
       <c r="G14" t="n">
-        <v>6.75383734703064</v>
+        <v>8.269646406173706</v>
       </c>
       <c r="H14" t="n">
-        <v>7.327933073043823</v>
+        <v>7.843109130859375</v>
       </c>
       <c r="I14" t="n">
-        <v>7.273491621017456</v>
+        <v>7.334821462631226</v>
       </c>
       <c r="J14" t="n">
-        <v>7.306914091110229</v>
+        <v>9.170196533203125</v>
       </c>
       <c r="K14" t="n">
-        <v>7.596699237823486</v>
+        <v>8.556221485137939</v>
       </c>
       <c r="L14" t="n">
-        <v>7.39410707950592</v>
+        <v>7.937862992286682</v>
       </c>
     </row>
     <row r="15">
@@ -2956,37 +2956,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>6.79874062538147</v>
+        <v>6.59123706817627</v>
       </c>
       <c r="C15" t="n">
-        <v>6.843576431274414</v>
+        <v>6.550817966461182</v>
       </c>
       <c r="D15" t="n">
-        <v>6.682620525360107</v>
+        <v>6.938827753067017</v>
       </c>
       <c r="E15" t="n">
-        <v>6.798736572265625</v>
+        <v>7.316893577575684</v>
       </c>
       <c r="F15" t="n">
-        <v>6.975767374038696</v>
+        <v>6.541345834732056</v>
       </c>
       <c r="G15" t="n">
-        <v>7.575743198394775</v>
+        <v>6.657072782516479</v>
       </c>
       <c r="H15" t="n">
-        <v>6.565349817276001</v>
+        <v>6.705427885055542</v>
       </c>
       <c r="I15" t="n">
-        <v>6.883484840393066</v>
+        <v>6.619186878204346</v>
       </c>
       <c r="J15" t="n">
-        <v>6.708443641662598</v>
+        <v>7.598667144775391</v>
       </c>
       <c r="K15" t="n">
-        <v>6.617230892181396</v>
+        <v>6.601216554641724</v>
       </c>
       <c r="L15" t="n">
-        <v>6.844969391822815</v>
+        <v>6.812069344520569</v>
       </c>
     </row>
     <row r="16">
@@ -2994,37 +2994,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>6.944318532943726</v>
+        <v>6.721383571624756</v>
       </c>
       <c r="C16" t="n">
-        <v>6.753353834152222</v>
+        <v>7.485916614532471</v>
       </c>
       <c r="D16" t="n">
-        <v>6.981287240982056</v>
+        <v>9.0455002784729</v>
       </c>
       <c r="E16" t="n">
-        <v>6.706424236297607</v>
+        <v>10.34719514846802</v>
       </c>
       <c r="F16" t="n">
-        <v>7.175260305404663</v>
+        <v>7.755752801895142</v>
       </c>
       <c r="G16" t="n">
-        <v>7.718893766403198</v>
+        <v>6.926894664764404</v>
       </c>
       <c r="H16" t="n">
-        <v>7.339844465255737</v>
+        <v>6.868030548095703</v>
       </c>
       <c r="I16" t="n">
-        <v>6.532398223876953</v>
+        <v>6.876489162445068</v>
       </c>
       <c r="J16" t="n">
-        <v>6.885475397109985</v>
+        <v>6.387744903564453</v>
       </c>
       <c r="K16" t="n">
-        <v>10.25843191146851</v>
+        <v>6.57628345489502</v>
       </c>
       <c r="L16" t="n">
-        <v>7.329568791389465</v>
+        <v>7.499119114875794</v>
       </c>
     </row>
     <row r="17">
@@ -3032,37 +3032,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>6.982272624969482</v>
+        <v>8.300194263458252</v>
       </c>
       <c r="C17" t="n">
-        <v>7.893950223922729</v>
+        <v>8.685893058776855</v>
       </c>
       <c r="D17" t="n">
-        <v>8.153010606765747</v>
+        <v>6.854045629501343</v>
       </c>
       <c r="E17" t="n">
-        <v>7.992748260498047</v>
+        <v>7.904417753219604</v>
       </c>
       <c r="F17" t="n">
-        <v>7.684522151947021</v>
+        <v>7.20030403137207</v>
       </c>
       <c r="G17" t="n">
-        <v>6.98784065246582</v>
+        <v>6.807421207427979</v>
       </c>
       <c r="H17" t="n">
-        <v>6.874160289764404</v>
+        <v>7.536425828933716</v>
       </c>
       <c r="I17" t="n">
-        <v>7.841985940933228</v>
+        <v>7.271219968795776</v>
       </c>
       <c r="J17" t="n">
-        <v>7.511698484420776</v>
+        <v>7.39877462387085</v>
       </c>
       <c r="K17" t="n">
-        <v>7.616205215454102</v>
+        <v>7.227213144302368</v>
       </c>
       <c r="L17" t="n">
-        <v>7.553839445114136</v>
+        <v>7.518590950965882</v>
       </c>
     </row>
     <row r="18">
@@ -3070,37 +3070,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>7.268114566802979</v>
+        <v>6.843207597732544</v>
       </c>
       <c r="C18" t="n">
-        <v>6.501614093780518</v>
+        <v>6.630264520645142</v>
       </c>
       <c r="D18" t="n">
-        <v>7.443686246871948</v>
+        <v>6.87016749382019</v>
       </c>
       <c r="E18" t="n">
-        <v>6.724026918411255</v>
+        <v>6.598848819732666</v>
       </c>
       <c r="F18" t="n">
-        <v>6.570969343185425</v>
+        <v>6.578906536102295</v>
       </c>
       <c r="G18" t="n">
-        <v>6.605897426605225</v>
+        <v>7.474568128585815</v>
       </c>
       <c r="H18" t="n">
-        <v>7.511019706726074</v>
+        <v>6.395388126373291</v>
       </c>
       <c r="I18" t="n">
-        <v>10.48474621772766</v>
+        <v>6.841271638870239</v>
       </c>
       <c r="J18" t="n">
-        <v>6.276176691055298</v>
+        <v>6.229799270629883</v>
       </c>
       <c r="K18" t="n">
-        <v>7.634151220321655</v>
+        <v>6.592945337295532</v>
       </c>
       <c r="L18" t="n">
-        <v>7.302040243148804</v>
+        <v>6.70553674697876</v>
       </c>
     </row>
     <row r="19">
@@ -3108,37 +3108,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>6.429831743240356</v>
+        <v>6.315778970718384</v>
       </c>
       <c r="C19" t="n">
-        <v>6.659698009490967</v>
+        <v>7.525336265563965</v>
       </c>
       <c r="D19" t="n">
-        <v>6.561455726623535</v>
+        <v>6.320918321609497</v>
       </c>
       <c r="E19" t="n">
-        <v>6.159987926483154</v>
+        <v>6.509413719177246</v>
       </c>
       <c r="F19" t="n">
-        <v>6.563474178314209</v>
+        <v>6.639612674713135</v>
       </c>
       <c r="G19" t="n">
-        <v>6.393393039703369</v>
+        <v>5.985340356826782</v>
       </c>
       <c r="H19" t="n">
-        <v>6.333044528961182</v>
+        <v>7.077114105224609</v>
       </c>
       <c r="I19" t="n">
-        <v>7.663383483886719</v>
+        <v>6.321055173873901</v>
       </c>
       <c r="J19" t="n">
-        <v>10.71048331260681</v>
+        <v>6.25527548789978</v>
       </c>
       <c r="K19" t="n">
-        <v>7.917361974716187</v>
+        <v>7.099569320678711</v>
       </c>
       <c r="L19" t="n">
-        <v>7.139211392402649</v>
+        <v>6.604941439628601</v>
       </c>
     </row>
     <row r="20">
@@ -3146,37 +3146,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>6.493985414505005</v>
+        <v>9.580595016479492</v>
       </c>
       <c r="C20" t="n">
-        <v>7.763255596160889</v>
+        <v>8.704371452331543</v>
       </c>
       <c r="D20" t="n">
-        <v>7.067644357681274</v>
+        <v>7.61321234703064</v>
       </c>
       <c r="E20" t="n">
-        <v>6.743015766143799</v>
+        <v>7.246673107147217</v>
       </c>
       <c r="F20" t="n">
-        <v>7.011796712875366</v>
+        <v>7.302883386611938</v>
       </c>
       <c r="G20" t="n">
-        <v>6.741487741470337</v>
+        <v>6.823786735534668</v>
       </c>
       <c r="H20" t="n">
-        <v>6.963430881500244</v>
+        <v>10.59797024726868</v>
       </c>
       <c r="I20" t="n">
-        <v>7.375863552093506</v>
+        <v>8.435895442962646</v>
       </c>
       <c r="J20" t="n">
-        <v>7.107033014297485</v>
+        <v>7.028223037719727</v>
       </c>
       <c r="K20" t="n">
-        <v>6.818282127380371</v>
+        <v>6.58537220954895</v>
       </c>
       <c r="L20" t="n">
-        <v>7.008579516410828</v>
+        <v>7.99189829826355</v>
       </c>
     </row>
     <row r="21">
@@ -3184,37 +3184,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>7.80573296546936</v>
+        <v>7.036594152450562</v>
       </c>
       <c r="C21" t="n">
-        <v>7.34841513633728</v>
+        <v>6.760317087173462</v>
       </c>
       <c r="D21" t="n">
-        <v>6.868706941604614</v>
+        <v>7.320813894271851</v>
       </c>
       <c r="E21" t="n">
-        <v>7.307857751846313</v>
+        <v>6.924861431121826</v>
       </c>
       <c r="F21" t="n">
-        <v>6.832608699798584</v>
+        <v>7.079011678695679</v>
       </c>
       <c r="G21" t="n">
-        <v>10.03443789482117</v>
+        <v>7.561872243881226</v>
       </c>
       <c r="H21" t="n">
-        <v>7.507394313812256</v>
+        <v>7.165382385253906</v>
       </c>
       <c r="I21" t="n">
-        <v>8.121861457824707</v>
+        <v>7.031754970550537</v>
       </c>
       <c r="J21" t="n">
-        <v>6.715446949005127</v>
+        <v>7.010761737823486</v>
       </c>
       <c r="K21" t="n">
-        <v>7.902436971664429</v>
+        <v>6.886633157730103</v>
       </c>
       <c r="L21" t="n">
-        <v>7.644489908218384</v>
+        <v>7.077800273895264</v>
       </c>
     </row>
     <row r="22">
@@ -3222,37 +3222,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>5.557361125946045</v>
+        <v>5.967977523803711</v>
       </c>
       <c r="C22" t="n">
-        <v>5.525444030761719</v>
+        <v>5.721626043319702</v>
       </c>
       <c r="D22" t="n">
-        <v>5.883548974990845</v>
+        <v>5.83833909034729</v>
       </c>
       <c r="E22" t="n">
-        <v>5.927427053451538</v>
+        <v>6.254762172698975</v>
       </c>
       <c r="F22" t="n">
-        <v>5.785289525985718</v>
+        <v>7.310494422912598</v>
       </c>
       <c r="G22" t="n">
-        <v>5.982771158218384</v>
+        <v>6.650787115097046</v>
       </c>
       <c r="H22" t="n">
-        <v>5.421231508255005</v>
+        <v>6.399287939071655</v>
       </c>
       <c r="I22" t="n">
-        <v>6.261129856109619</v>
+        <v>6.458232641220093</v>
       </c>
       <c r="J22" t="n">
-        <v>6.056214809417725</v>
+        <v>5.771015167236328</v>
       </c>
       <c r="K22" t="n">
-        <v>6.579525470733643</v>
+        <v>6.818268775939941</v>
       </c>
       <c r="L22" t="n">
-        <v>5.897994351387024</v>
+        <v>6.319079089164734</v>
       </c>
     </row>
     <row r="23">
@@ -3260,37 +3260,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>7.768845796585083</v>
+        <v>7.292541265487671</v>
       </c>
       <c r="C23" t="n">
-        <v>8.240583658218384</v>
+        <v>7.319498062133789</v>
       </c>
       <c r="D23" t="n">
-        <v>9.208115816116333</v>
+        <v>8.981163501739502</v>
       </c>
       <c r="E23" t="n">
-        <v>7.256149053573608</v>
+        <v>7.865092277526855</v>
       </c>
       <c r="F23" t="n">
-        <v>8.275999069213867</v>
+        <v>7.310489177703857</v>
       </c>
       <c r="G23" t="n">
-        <v>9.442492485046387</v>
+        <v>7.889993906021118</v>
       </c>
       <c r="H23" t="n">
-        <v>7.807729482650757</v>
+        <v>7.089577674865723</v>
       </c>
       <c r="I23" t="n">
-        <v>9.902765274047852</v>
+        <v>6.878604173660278</v>
       </c>
       <c r="J23" t="n">
-        <v>9.638183355331421</v>
+        <v>7.291543006896973</v>
       </c>
       <c r="K23" t="n">
-        <v>8.607087850570679</v>
+        <v>24.2282886505127</v>
       </c>
       <c r="L23" t="n">
-        <v>8.614795184135437</v>
+        <v>9.214679169654847</v>
       </c>
     </row>
     <row r="24">
@@ -3298,37 +3298,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>7.315892219543457</v>
+        <v>7.94226861000061</v>
       </c>
       <c r="C24" t="n">
-        <v>7.285955905914307</v>
+        <v>6.601203203201294</v>
       </c>
       <c r="D24" t="n">
-        <v>9.386597633361816</v>
+        <v>6.915894985198975</v>
       </c>
       <c r="E24" t="n">
-        <v>7.474513053894043</v>
+        <v>9.848436594009399</v>
       </c>
       <c r="F24" t="n">
-        <v>8.927834987640381</v>
+        <v>7.115406513214111</v>
       </c>
       <c r="G24" t="n">
-        <v>6.726412296295166</v>
+        <v>7.664473533630371</v>
       </c>
       <c r="H24" t="n">
-        <v>7.163796186447144</v>
+        <v>6.964770793914795</v>
       </c>
       <c r="I24" t="n">
-        <v>7.315893650054932</v>
+        <v>8.263500213623047</v>
       </c>
       <c r="J24" t="n">
-        <v>7.579193592071533</v>
+        <v>7.312861442565918</v>
       </c>
       <c r="K24" t="n">
-        <v>6.928855419158936</v>
+        <v>7.093433141708374</v>
       </c>
       <c r="L24" t="n">
-        <v>7.610494494438171</v>
+        <v>7.572224903106689</v>
       </c>
     </row>
     <row r="25">
@@ -3336,37 +3336,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>6.367305994033813</v>
+        <v>6.496943473815918</v>
       </c>
       <c r="C25" t="n">
-        <v>7.278037548065186</v>
+        <v>6.346343994140625</v>
       </c>
       <c r="D25" t="n">
-        <v>6.723015785217285</v>
+        <v>6.554794788360596</v>
       </c>
       <c r="E25" t="n">
-        <v>6.798333168029785</v>
+        <v>6.477020025253296</v>
       </c>
       <c r="F25" t="n">
-        <v>6.763959884643555</v>
+        <v>6.685466051101685</v>
       </c>
       <c r="G25" t="n">
-        <v>7.488061189651489</v>
+        <v>6.529871225357056</v>
       </c>
       <c r="H25" t="n">
-        <v>7.085174798965454</v>
+        <v>6.890004634857178</v>
       </c>
       <c r="I25" t="n">
-        <v>7.178848505020142</v>
+        <v>6.805753946304321</v>
       </c>
       <c r="J25" t="n">
-        <v>8.749764204025269</v>
+        <v>9.359166622161865</v>
       </c>
       <c r="K25" t="n">
-        <v>6.564955949783325</v>
+        <v>6.656067848205566</v>
       </c>
       <c r="L25" t="n">
-        <v>7.09974570274353</v>
+        <v>6.88014326095581</v>
       </c>
     </row>
     <row r="26">
@@ -3374,37 +3374,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>7.31235408782959</v>
+        <v>6.647624015808105</v>
       </c>
       <c r="C26" t="n">
-        <v>6.940975904464722</v>
+        <v>6.051250457763672</v>
       </c>
       <c r="D26" t="n">
-        <v>6.650708198547363</v>
+        <v>6.780579090118408</v>
       </c>
       <c r="E26" t="n">
-        <v>6.447150945663452</v>
+        <v>6.166468381881714</v>
       </c>
       <c r="F26" t="n">
-        <v>6.858087539672852</v>
+        <v>6.691112279891968</v>
       </c>
       <c r="G26" t="n">
-        <v>6.51294207572937</v>
+        <v>7.077108383178711</v>
       </c>
       <c r="H26" t="n">
-        <v>6.338471174240112</v>
+        <v>6.610827445983887</v>
       </c>
       <c r="I26" t="n">
-        <v>6.637108087539673</v>
+        <v>6.315306425094604</v>
       </c>
       <c r="J26" t="n">
-        <v>6.191294193267822</v>
+        <v>6.354338884353638</v>
       </c>
       <c r="K26" t="n">
-        <v>7.105435848236084</v>
+        <v>7.064049482345581</v>
       </c>
       <c r="L26" t="n">
-        <v>6.699452805519104</v>
+        <v>6.575866484642029</v>
       </c>
     </row>
     <row r="27">
@@ -3412,37 +3412,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>7.219991683959961</v>
+        <v>7.077969551086426</v>
       </c>
       <c r="C27" t="n">
-        <v>9.224065542221069</v>
+        <v>6.871009349822998</v>
       </c>
       <c r="D27" t="n">
-        <v>8.169761419296265</v>
+        <v>6.914891242980957</v>
       </c>
       <c r="E27" t="n">
-        <v>10.11568093299866</v>
+        <v>10.11276817321777</v>
       </c>
       <c r="F27" t="n">
-        <v>7.269680023193359</v>
+        <v>7.266509056091309</v>
       </c>
       <c r="G27" t="n">
-        <v>7.181339979171753</v>
+        <v>9.027985572814941</v>
       </c>
       <c r="H27" t="n">
-        <v>7.51600170135498</v>
+        <v>6.536877870559692</v>
       </c>
       <c r="I27" t="n">
-        <v>10.07978010177612</v>
+        <v>9.186651229858398</v>
       </c>
       <c r="J27" t="n">
-        <v>7.258639335632324</v>
+        <v>7.592646360397339</v>
       </c>
       <c r="K27" t="n">
-        <v>8.262517690658569</v>
+        <v>7.079010725021362</v>
       </c>
       <c r="L27" t="n">
-        <v>8.229745841026306</v>
+        <v>7.76663191318512</v>
       </c>
     </row>
     <row r="28">
@@ -3450,37 +3450,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>7.797765731811523</v>
+        <v>7.158332347869873</v>
       </c>
       <c r="C28" t="n">
-        <v>9.885824918746948</v>
+        <v>7.673986911773682</v>
       </c>
       <c r="D28" t="n">
-        <v>7.378763198852539</v>
+        <v>7.229592323303223</v>
       </c>
       <c r="E28" t="n">
-        <v>7.24208927154541</v>
+        <v>7.800652742385864</v>
       </c>
       <c r="F28" t="n">
-        <v>7.916405439376831</v>
+        <v>7.598659753799438</v>
       </c>
       <c r="G28" t="n">
-        <v>9.087877511978149</v>
+        <v>7.820106506347656</v>
       </c>
       <c r="H28" t="n">
-        <v>9.25046443939209</v>
+        <v>8.511811256408691</v>
       </c>
       <c r="I28" t="n">
-        <v>7.277015686035156</v>
+        <v>7.343817710876465</v>
       </c>
       <c r="J28" t="n">
-        <v>7.963752746582031</v>
+        <v>6.974745988845825</v>
       </c>
       <c r="K28" t="n">
-        <v>6.987735033035278</v>
+        <v>7.716848611831665</v>
       </c>
       <c r="L28" t="n">
-        <v>8.078769397735595</v>
+        <v>7.582855415344238</v>
       </c>
     </row>
     <row r="29">
@@ -3488,37 +3488,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>7.145355701446533</v>
+        <v>7.545315027236938</v>
       </c>
       <c r="C29" t="n">
-        <v>7.822107315063477</v>
+        <v>7.027663707733154</v>
       </c>
       <c r="D29" t="n">
-        <v>6.843596696853638</v>
+        <v>7.133352279663086</v>
       </c>
       <c r="E29" t="n">
-        <v>8.007642030715942</v>
+        <v>7.37135648727417</v>
       </c>
       <c r="F29" t="n">
-        <v>10.95236873626709</v>
+        <v>7.246059656143188</v>
       </c>
       <c r="G29" t="n">
-        <v>7.873059511184692</v>
+        <v>6.78424596786499</v>
       </c>
       <c r="H29" t="n">
-        <v>6.844250679016113</v>
+        <v>7.063543558120728</v>
       </c>
       <c r="I29" t="n">
-        <v>7.066143989562988</v>
+        <v>7.686436414718628</v>
       </c>
       <c r="J29" t="n">
-        <v>7.467657804489136</v>
+        <v>8.011549472808838</v>
       </c>
       <c r="K29" t="n">
-        <v>7.182287693023682</v>
+        <v>7.839612007141113</v>
       </c>
       <c r="L29" t="n">
-        <v>7.720447015762329</v>
+        <v>7.370913457870484</v>
       </c>
     </row>
     <row r="30">
@@ -3526,37 +3526,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>7.697923898696899</v>
+        <v>9.360982656478882</v>
       </c>
       <c r="C30" t="n">
-        <v>7.196714878082275</v>
+        <v>8.989344596862793</v>
       </c>
       <c r="D30" t="n">
-        <v>7.709897756576538</v>
+        <v>8.722693204879761</v>
       </c>
       <c r="E30" t="n">
-        <v>7.181210041046143</v>
+        <v>8.670134782791138</v>
       </c>
       <c r="F30" t="n">
-        <v>7.563762426376343</v>
+        <v>9.739387035369873</v>
       </c>
       <c r="G30" t="n">
-        <v>9.109344482421875</v>
+        <v>8.427834272384644</v>
       </c>
       <c r="H30" t="n">
-        <v>7.113457202911377</v>
+        <v>7.60798168182373</v>
       </c>
       <c r="I30" t="n">
-        <v>9.333745002746582</v>
+        <v>7.160690069198608</v>
       </c>
       <c r="J30" t="n">
-        <v>8.506840467453003</v>
+        <v>7.556279420852661</v>
       </c>
       <c r="K30" t="n">
-        <v>7.700384140014648</v>
+        <v>7.156811475753784</v>
       </c>
       <c r="L30" t="n">
-        <v>7.911328029632569</v>
+        <v>8.339213919639587</v>
       </c>
     </row>
     <row r="31">
@@ -3564,37 +3564,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>7.063091039657593</v>
+        <v>6.939838171005249</v>
       </c>
       <c r="C31" t="n">
-        <v>9.195608139038086</v>
+        <v>6.94282341003418</v>
       </c>
       <c r="D31" t="n">
-        <v>7.276473045349121</v>
+        <v>7.026652574539185</v>
       </c>
       <c r="E31" t="n">
-        <v>6.300464868545532</v>
+        <v>7.032107353210449</v>
       </c>
       <c r="F31" t="n">
-        <v>7.49445652961731</v>
+        <v>6.93585467338562</v>
       </c>
       <c r="G31" t="n">
-        <v>6.348354578018188</v>
+        <v>7.66274881362915</v>
       </c>
       <c r="H31" t="n">
-        <v>6.911908864974976</v>
+        <v>7.937870264053345</v>
       </c>
       <c r="I31" t="n">
-        <v>6.531418085098267</v>
+        <v>6.583927154541016</v>
       </c>
       <c r="J31" t="n">
-        <v>7.02121901512146</v>
+        <v>6.673421621322632</v>
       </c>
       <c r="K31" t="n">
-        <v>8.19774317741394</v>
+        <v>7.919344663619995</v>
       </c>
       <c r="L31" t="n">
-        <v>7.234073734283447</v>
+        <v>7.165458869934082</v>
       </c>
     </row>
     <row r="32">
@@ -3602,37 +3602,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>6.613166332244873</v>
+        <v>6.703476905822754</v>
       </c>
       <c r="C32" t="n">
-        <v>8.54735541343689</v>
+        <v>8.577689170837402</v>
       </c>
       <c r="D32" t="n">
-        <v>6.712482452392578</v>
+        <v>7.013937711715698</v>
       </c>
       <c r="E32" t="n">
-        <v>8.996681928634644</v>
+        <v>6.796353101730347</v>
       </c>
       <c r="F32" t="n">
-        <v>6.416683673858643</v>
+        <v>6.631134033203125</v>
       </c>
       <c r="G32" t="n">
-        <v>9.257957220077515</v>
+        <v>7.08002233505249</v>
       </c>
       <c r="H32" t="n">
-        <v>9.122263193130493</v>
+        <v>6.132441997528076</v>
       </c>
       <c r="I32" t="n">
-        <v>9.336753368377686</v>
+        <v>6.379199028015137</v>
       </c>
       <c r="J32" t="n">
-        <v>6.125903844833374</v>
+        <v>6.452592134475708</v>
       </c>
       <c r="K32" t="n">
-        <v>6.768815279006958</v>
+        <v>6.76689887046814</v>
       </c>
       <c r="L32" t="n">
-        <v>7.789806270599366</v>
+        <v>6.853374528884888</v>
       </c>
     </row>
     <row r="33">
@@ -3640,37 +3640,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>6.8376305103302</v>
+        <v>6.559781312942505</v>
       </c>
       <c r="C33" t="n">
-        <v>7.518369197845459</v>
+        <v>7.297932147979736</v>
       </c>
       <c r="D33" t="n">
-        <v>6.745334148406982</v>
+        <v>6.9059739112854</v>
       </c>
       <c r="E33" t="n">
-        <v>7.432678699493408</v>
+        <v>7.098465204238892</v>
       </c>
       <c r="F33" t="n">
-        <v>7.770713806152344</v>
+        <v>7.059035062789917</v>
       </c>
       <c r="G33" t="n">
-        <v>6.770793676376343</v>
+        <v>7.149839162826538</v>
       </c>
       <c r="H33" t="n">
-        <v>6.738380908966064</v>
+        <v>7.212664604187012</v>
       </c>
       <c r="I33" t="n">
-        <v>7.669543266296387</v>
+        <v>9.189154624938965</v>
       </c>
       <c r="J33" t="n">
-        <v>7.207661867141724</v>
+        <v>6.884150505065918</v>
       </c>
       <c r="K33" t="n">
-        <v>7.038310527801514</v>
+        <v>6.860248565673828</v>
       </c>
       <c r="L33" t="n">
-        <v>7.172941660881042</v>
+        <v>7.221724510192871</v>
       </c>
     </row>
     <row r="34">
@@ -3678,37 +3678,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>6.114598751068115</v>
+        <v>5.918645143508911</v>
       </c>
       <c r="C34" t="n">
-        <v>6.150021553039551</v>
+        <v>6.02736496925354</v>
       </c>
       <c r="D34" t="n">
-        <v>6.414634466171265</v>
+        <v>8.564268827438354</v>
       </c>
       <c r="E34" t="n">
-        <v>6.838601350784302</v>
+        <v>6.100699901580811</v>
       </c>
       <c r="F34" t="n">
-        <v>8.112849235534668</v>
+        <v>6.173956632614136</v>
       </c>
       <c r="G34" t="n">
-        <v>6.482018947601318</v>
+        <v>6.173479557037354</v>
       </c>
       <c r="H34" t="n">
-        <v>7.200154781341553</v>
+        <v>6.653213262557983</v>
       </c>
       <c r="I34" t="n">
-        <v>6.332425355911255</v>
+        <v>6.131378650665283</v>
       </c>
       <c r="J34" t="n">
-        <v>6.282041788101196</v>
+        <v>6.303540468215942</v>
       </c>
       <c r="K34" t="n">
-        <v>6.081022262573242</v>
+        <v>6.362297296524048</v>
       </c>
       <c r="L34" t="n">
-        <v>6.600836849212646</v>
+        <v>6.440884470939636</v>
       </c>
     </row>
     <row r="35">
@@ -3716,37 +3716,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>7.782208442687988</v>
+        <v>7.597671985626221</v>
       </c>
       <c r="C35" t="n">
-        <v>7.369764804840088</v>
+        <v>7.279039859771729</v>
       </c>
       <c r="D35" t="n">
-        <v>7.44659686088562</v>
+        <v>7.710880994796753</v>
       </c>
       <c r="E35" t="n">
-        <v>7.813110113143921</v>
+        <v>7.524417400360107</v>
       </c>
       <c r="F35" t="n">
-        <v>7.449046611785889</v>
+        <v>7.23064398765564</v>
       </c>
       <c r="G35" t="n">
-        <v>9.553231239318848</v>
+        <v>7.114436626434326</v>
       </c>
       <c r="H35" t="n">
-        <v>7.318881273269653</v>
+        <v>7.596736907958984</v>
       </c>
       <c r="I35" t="n">
-        <v>6.986498355865479</v>
+        <v>7.607674837112427</v>
       </c>
       <c r="J35" t="n">
-        <v>6.983250141143799</v>
+        <v>7.178216218948364</v>
       </c>
       <c r="K35" t="n">
-        <v>7.339861869812012</v>
+        <v>7.469513893127441</v>
       </c>
       <c r="L35" t="n">
-        <v>7.60424497127533</v>
+        <v>7.430923271179199</v>
       </c>
     </row>
     <row r="36">
@@ -3754,37 +3754,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>8.964213371276855</v>
+        <v>8.37867546081543</v>
       </c>
       <c r="C36" t="n">
-        <v>7.965230464935303</v>
+        <v>9.457936763763428</v>
       </c>
       <c r="D36" t="n">
-        <v>7.492462873458862</v>
+        <v>8.963690996170044</v>
       </c>
       <c r="E36" t="n">
-        <v>9.005070209503174</v>
+        <v>9.717815160751343</v>
       </c>
       <c r="F36" t="n">
-        <v>8.181674242019653</v>
+        <v>8.811584949493408</v>
       </c>
       <c r="G36" t="n">
-        <v>7.457535982131958</v>
+        <v>8.039590835571289</v>
       </c>
       <c r="H36" t="n">
-        <v>8.998692035675049</v>
+        <v>7.767747402191162</v>
       </c>
       <c r="I36" t="n">
-        <v>7.591192007064819</v>
+        <v>8.219708442687988</v>
       </c>
       <c r="J36" t="n">
-        <v>7.839566707611084</v>
+        <v>8.051366567611694</v>
       </c>
       <c r="K36" t="n">
-        <v>8.557731628417969</v>
+        <v>7.787881374359131</v>
       </c>
       <c r="L36" t="n">
-        <v>8.205336952209473</v>
+        <v>8.519599795341492</v>
       </c>
     </row>
     <row r="37">
@@ -3792,37 +3792,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>6.983244895935059</v>
+        <v>6.987335681915283</v>
       </c>
       <c r="C37" t="n">
-        <v>6.054611206054688</v>
+        <v>6.841031789779663</v>
       </c>
       <c r="D37" t="n">
-        <v>6.259594678878784</v>
+        <v>6.599894762039185</v>
       </c>
       <c r="E37" t="n">
-        <v>6.28100848197937</v>
+        <v>10.63634657859802</v>
       </c>
       <c r="F37" t="n">
-        <v>5.716973781585693</v>
+        <v>7.916167974472046</v>
       </c>
       <c r="G37" t="n">
-        <v>5.988859891891479</v>
+        <v>7.981396198272705</v>
       </c>
       <c r="H37" t="n">
-        <v>7.080113887786865</v>
+        <v>7.307095527648926</v>
       </c>
       <c r="I37" t="n">
-        <v>6.170530557632446</v>
+        <v>7.096689939498901</v>
       </c>
       <c r="J37" t="n">
-        <v>5.867567300796509</v>
+        <v>6.406637668609619</v>
       </c>
       <c r="K37" t="n">
-        <v>6.398744583129883</v>
+        <v>7.269672393798828</v>
       </c>
       <c r="L37" t="n">
-        <v>6.280124926567078</v>
+        <v>7.504226851463318</v>
       </c>
     </row>
     <row r="38">
@@ -3830,37 +3830,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>6.769298076629639</v>
+        <v>7.291568517684937</v>
       </c>
       <c r="C38" t="n">
-        <v>6.693470001220703</v>
+        <v>6.699110507965088</v>
       </c>
       <c r="D38" t="n">
-        <v>6.663531303405762</v>
+        <v>6.926555395126343</v>
       </c>
       <c r="E38" t="n">
-        <v>8.306579351425171</v>
+        <v>6.915429353713989</v>
       </c>
       <c r="F38" t="n">
-        <v>6.944659471511841</v>
+        <v>6.760320901870728</v>
       </c>
       <c r="G38" t="n">
-        <v>7.071016311645508</v>
+        <v>6.661401987075806</v>
       </c>
       <c r="H38" t="n">
-        <v>6.458091974258423</v>
+        <v>7.381539344787598</v>
       </c>
       <c r="I38" t="n">
-        <v>7.396159887313843</v>
+        <v>6.760438442230225</v>
       </c>
       <c r="J38" t="n">
-        <v>6.627165555953979</v>
+        <v>7.286108732223511</v>
       </c>
       <c r="K38" t="n">
-        <v>8.725338935852051</v>
+        <v>6.993847370147705</v>
       </c>
       <c r="L38" t="n">
-        <v>7.165531086921692</v>
+        <v>6.967632055282593</v>
       </c>
     </row>
     <row r="39">
@@ -3868,37 +3868,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>6.755829572677612</v>
+        <v>7.260658264160156</v>
       </c>
       <c r="C39" t="n">
-        <v>6.498452186584473</v>
+        <v>6.940474271774292</v>
       </c>
       <c r="D39" t="n">
-        <v>6.317449808120728</v>
+        <v>7.760799169540405</v>
       </c>
       <c r="E39" t="n">
-        <v>6.679508447647095</v>
+        <v>6.473093509674072</v>
       </c>
       <c r="F39" t="n">
-        <v>6.101019382476807</v>
+        <v>7.132820606231689</v>
       </c>
       <c r="G39" t="n">
-        <v>6.330436229705811</v>
+        <v>6.345554351806641</v>
       </c>
       <c r="H39" t="n">
-        <v>8.766707181930542</v>
+        <v>7.507716417312622</v>
       </c>
       <c r="I39" t="n">
-        <v>6.951874256134033</v>
+        <v>7.166804552078247</v>
       </c>
       <c r="J39" t="n">
-        <v>6.518924713134766</v>
+        <v>6.565769195556641</v>
       </c>
       <c r="K39" t="n">
-        <v>7.065171241760254</v>
+        <v>7.333937406539917</v>
       </c>
       <c r="L39" t="n">
-        <v>6.798537302017212</v>
+        <v>7.048762774467468</v>
       </c>
     </row>
     <row r="40">
@@ -3906,37 +3906,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>7.084977626800537</v>
+        <v>10.88643717765808</v>
       </c>
       <c r="C40" t="n">
-        <v>7.020143032073975</v>
+        <v>7.917413711547852</v>
       </c>
       <c r="D40" t="n">
-        <v>6.524902820587158</v>
+        <v>8.094362497329712</v>
       </c>
       <c r="E40" t="n">
-        <v>6.803719997406006</v>
+        <v>8.026175498962402</v>
       </c>
       <c r="F40" t="n">
-        <v>8.737256288528442</v>
+        <v>12.20139193534851</v>
       </c>
       <c r="G40" t="n">
-        <v>6.385776519775391</v>
+        <v>7.447694301605225</v>
       </c>
       <c r="H40" t="n">
-        <v>7.287962436676025</v>
+        <v>9.574588537216187</v>
       </c>
       <c r="I40" t="n">
-        <v>6.639105081558228</v>
+        <v>8.490086793899536</v>
       </c>
       <c r="J40" t="n">
-        <v>7.574720859527588</v>
+        <v>7.885954141616821</v>
       </c>
       <c r="K40" t="n">
-        <v>6.578778028488159</v>
+        <v>7.745307683944702</v>
       </c>
       <c r="L40" t="n">
-        <v>7.063734269142151</v>
+        <v>8.826941227912902</v>
       </c>
     </row>
     <row r="41">
@@ -3944,37 +3944,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>7.729854106903076</v>
+        <v>8.109279870986938</v>
       </c>
       <c r="C41" t="n">
-        <v>8.363228559494019</v>
+        <v>7.327469825744629</v>
       </c>
       <c r="D41" t="n">
-        <v>7.236057758331299</v>
+        <v>9.959643363952637</v>
       </c>
       <c r="E41" t="n">
-        <v>8.621140480041504</v>
+        <v>9.156728744506836</v>
       </c>
       <c r="F41" t="n">
-        <v>7.941420078277588</v>
+        <v>10.86824202537537</v>
       </c>
       <c r="G41" t="n">
-        <v>7.461647987365723</v>
+        <v>7.051126956939697</v>
       </c>
       <c r="H41" t="n">
-        <v>7.729427099227905</v>
+        <v>7.775224924087524</v>
       </c>
       <c r="I41" t="n">
-        <v>7.274601221084595</v>
+        <v>10.04247450828552</v>
       </c>
       <c r="J41" t="n">
-        <v>7.838683366775513</v>
+        <v>7.954829692840576</v>
       </c>
       <c r="K41" t="n">
-        <v>7.741386890411377</v>
+        <v>7.289560317993164</v>
       </c>
       <c r="L41" t="n">
-        <v>7.79374475479126</v>
+        <v>8.55345802307129</v>
       </c>
     </row>
     <row r="42">
@@ -3982,37 +3982,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>5.61040472984314</v>
+        <v>6.057758808135986</v>
       </c>
       <c r="C42" t="n">
-        <v>6.437780857086182</v>
+        <v>5.607454538345337</v>
       </c>
       <c r="D42" t="n">
-        <v>6.276707649230957</v>
+        <v>5.926088333129883</v>
       </c>
       <c r="E42" t="n">
-        <v>5.550980091094971</v>
+        <v>6.525425672531128</v>
       </c>
       <c r="F42" t="n">
-        <v>6.212213277816772</v>
+        <v>5.853817462921143</v>
       </c>
       <c r="G42" t="n">
-        <v>6.55884313583374</v>
+        <v>5.93610143661499</v>
       </c>
       <c r="H42" t="n">
-        <v>6.010705232620239</v>
+        <v>6.008394002914429</v>
       </c>
       <c r="I42" t="n">
-        <v>5.920454978942871</v>
+        <v>5.692682266235352</v>
       </c>
       <c r="J42" t="n">
-        <v>5.629705190658569</v>
+        <v>5.634358406066895</v>
       </c>
       <c r="K42" t="n">
-        <v>5.730931997299194</v>
+        <v>5.758035659790039</v>
       </c>
       <c r="L42" t="n">
-        <v>5.993872714042664</v>
+        <v>5.900011658668518</v>
       </c>
     </row>
     <row r="43">
@@ -4020,37 +4020,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>6.7828369140625</v>
+        <v>8.065725088119507</v>
       </c>
       <c r="C43" t="n">
-        <v>7.084524154663086</v>
+        <v>6.475202560424805</v>
       </c>
       <c r="D43" t="n">
-        <v>7.041100025177002</v>
+        <v>7.686518430709839</v>
       </c>
       <c r="E43" t="n">
-        <v>6.215219497680664</v>
+        <v>7.006786346435547</v>
       </c>
       <c r="F43" t="n">
-        <v>6.494978904724121</v>
+        <v>6.77390193939209</v>
       </c>
       <c r="G43" t="n">
-        <v>6.843571424484253</v>
+        <v>6.450755834579468</v>
       </c>
       <c r="H43" t="n">
-        <v>7.005205392837524</v>
+        <v>6.871494770050049</v>
       </c>
       <c r="I43" t="n">
-        <v>6.591245889663696</v>
+        <v>7.841029644012451</v>
       </c>
       <c r="J43" t="n">
-        <v>6.855556726455688</v>
+        <v>6.384762763977051</v>
       </c>
       <c r="K43" t="n">
-        <v>7.886418104171753</v>
+        <v>6.77774977684021</v>
       </c>
       <c r="L43" t="n">
-        <v>6.880065703392029</v>
+        <v>7.033392715454101</v>
       </c>
     </row>
     <row r="44">
@@ -4058,37 +4058,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>6.751356601715088</v>
+        <v>7.841068983078003</v>
       </c>
       <c r="C44" t="n">
-        <v>6.817760229110718</v>
+        <v>6.976309299468994</v>
       </c>
       <c r="D44" t="n">
-        <v>6.991233587265015</v>
+        <v>7.588215351104736</v>
       </c>
       <c r="E44" t="n">
-        <v>8.581180095672607</v>
+        <v>7.96080470085144</v>
       </c>
       <c r="F44" t="n">
-        <v>7.141865491867065</v>
+        <v>6.673004865646362</v>
       </c>
       <c r="G44" t="n">
-        <v>6.86653470993042</v>
+        <v>6.639598846435547</v>
       </c>
       <c r="H44" t="n">
-        <v>6.850091457366943</v>
+        <v>7.310931921005249</v>
       </c>
       <c r="I44" t="n">
-        <v>9.284364223480225</v>
+        <v>7.259410381317139</v>
       </c>
       <c r="J44" t="n">
-        <v>6.67056679725647</v>
+        <v>6.619226932525635</v>
       </c>
       <c r="K44" t="n">
-        <v>6.509939908981323</v>
+        <v>7.065571784973145</v>
       </c>
       <c r="L44" t="n">
-        <v>7.246489310264588</v>
+        <v>7.193414306640625</v>
       </c>
     </row>
     <row r="45">
@@ -4096,37 +4096,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>9.005102634429932</v>
+        <v>8.723328113555908</v>
       </c>
       <c r="C45" t="n">
-        <v>6.891451358795166</v>
+        <v>7.578248739242554</v>
       </c>
       <c r="D45" t="n">
-        <v>7.210652351379395</v>
+        <v>8.19316840171814</v>
       </c>
       <c r="E45" t="n">
-        <v>6.712420225143433</v>
+        <v>8.077940225601196</v>
       </c>
       <c r="F45" t="n">
-        <v>9.589622020721436</v>
+        <v>6.921917200088501</v>
       </c>
       <c r="G45" t="n">
-        <v>7.814892053604126</v>
+        <v>7.503432035446167</v>
       </c>
       <c r="H45" t="n">
-        <v>7.210319757461548</v>
+        <v>7.058017492294312</v>
       </c>
       <c r="I45" t="n">
-        <v>7.253169536590576</v>
+        <v>8.714315176010132</v>
       </c>
       <c r="J45" t="n">
-        <v>7.829706192016602</v>
+        <v>7.432088375091553</v>
       </c>
       <c r="K45" t="n">
-        <v>6.869693040847778</v>
+        <v>7.146824359893799</v>
       </c>
       <c r="L45" t="n">
-        <v>7.638702917098999</v>
+        <v>7.734928011894226</v>
       </c>
     </row>
     <row r="46">
@@ -4134,37 +4134,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>7.018739461898804</v>
+        <v>6.927134037017822</v>
       </c>
       <c r="C46" t="n">
-        <v>6.830285787582397</v>
+        <v>7.356762647628784</v>
       </c>
       <c r="D46" t="n">
-        <v>6.832242488861084</v>
+        <v>7.465508222579956</v>
       </c>
       <c r="E46" t="n">
-        <v>6.962959051132202</v>
+        <v>6.96779727935791</v>
       </c>
       <c r="F46" t="n">
-        <v>7.39382004737854</v>
+        <v>6.864036083221436</v>
       </c>
       <c r="G46" t="n">
-        <v>7.004841327667236</v>
+        <v>6.859538316726685</v>
       </c>
       <c r="H46" t="n">
-        <v>6.612824678421021</v>
+        <v>7.66899299621582</v>
       </c>
       <c r="I46" t="n">
-        <v>7.798256635665894</v>
+        <v>8.285892963409424</v>
       </c>
       <c r="J46" t="n">
-        <v>7.264717578887939</v>
+        <v>7.561779499053955</v>
       </c>
       <c r="K46" t="n">
-        <v>6.870106220245361</v>
+        <v>7.306886434555054</v>
       </c>
       <c r="L46" t="n">
-        <v>7.058879327774048</v>
+        <v>7.326432847976685</v>
       </c>
     </row>
     <row r="47">
@@ -4172,37 +4172,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>7.301033973693848</v>
+        <v>8.622084856033325</v>
       </c>
       <c r="C47" t="n">
-        <v>7.13147759437561</v>
+        <v>6.989718914031982</v>
       </c>
       <c r="D47" t="n">
-        <v>6.648707628250122</v>
+        <v>7.840526819229126</v>
       </c>
       <c r="E47" t="n">
-        <v>8.70691990852356</v>
+        <v>7.352797508239746</v>
       </c>
       <c r="F47" t="n">
-        <v>8.290475606918335</v>
+        <v>8.621063947677612</v>
       </c>
       <c r="G47" t="n">
-        <v>7.12946891784668</v>
+        <v>7.581715822219849</v>
       </c>
       <c r="H47" t="n">
-        <v>7.053657054901123</v>
+        <v>8.000656127929688</v>
       </c>
       <c r="I47" t="n">
-        <v>6.753977537155151</v>
+        <v>7.110886812210083</v>
       </c>
       <c r="J47" t="n">
-        <v>6.720063924789429</v>
+        <v>7.396435737609863</v>
       </c>
       <c r="K47" t="n">
-        <v>6.977849721908569</v>
+        <v>8.333829879760742</v>
       </c>
       <c r="L47" t="n">
-        <v>7.271363186836242</v>
+        <v>7.784971642494201</v>
       </c>
     </row>
     <row r="48">
@@ -4210,37 +4210,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>6.992826223373413</v>
+        <v>6.631795883178711</v>
       </c>
       <c r="C48" t="n">
-        <v>7.345447063446045</v>
+        <v>6.155503034591675</v>
       </c>
       <c r="D48" t="n">
-        <v>7.205252170562744</v>
+        <v>7.010784387588501</v>
       </c>
       <c r="E48" t="n">
-        <v>6.197900295257568</v>
+        <v>9.036847352981567</v>
       </c>
       <c r="F48" t="n">
-        <v>7.67654824256897</v>
+        <v>7.095041990280151</v>
       </c>
       <c r="G48" t="n">
-        <v>6.606422424316406</v>
+        <v>6.434316158294678</v>
       </c>
       <c r="H48" t="n">
-        <v>6.746492385864258</v>
+        <v>6.488639116287231</v>
       </c>
       <c r="I48" t="n">
-        <v>10.17314171791077</v>
+        <v>6.823265790939331</v>
       </c>
       <c r="J48" t="n">
-        <v>7.005806922912598</v>
+        <v>6.647744417190552</v>
       </c>
       <c r="K48" t="n">
-        <v>6.153039455413818</v>
+        <v>6.779691457748413</v>
       </c>
       <c r="L48" t="n">
-        <v>7.210287690162659</v>
+        <v>6.910362958908081</v>
       </c>
     </row>
     <row r="49">
@@ -4248,37 +4248,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>7.711528778076172</v>
+        <v>6.698457479476929</v>
       </c>
       <c r="C49" t="n">
-        <v>7.803735494613647</v>
+        <v>7.419116020202637</v>
       </c>
       <c r="D49" t="n">
-        <v>9.061003923416138</v>
+        <v>6.90891170501709</v>
       </c>
       <c r="E49" t="n">
-        <v>7.422143936157227</v>
+        <v>6.894936561584473</v>
       </c>
       <c r="F49" t="n">
-        <v>8.033570528030396</v>
+        <v>7.310384035110474</v>
       </c>
       <c r="G49" t="n">
-        <v>7.307924270629883</v>
+        <v>7.110896110534668</v>
       </c>
       <c r="H49" t="n">
-        <v>7.119076490402222</v>
+        <v>7.054542064666748</v>
       </c>
       <c r="I49" t="n">
-        <v>7.710908174514771</v>
+        <v>6.764276266098022</v>
       </c>
       <c r="J49" t="n">
-        <v>7.451139450073242</v>
+        <v>6.634628772735596</v>
       </c>
       <c r="K49" t="n">
-        <v>7.741303443908691</v>
+        <v>7.46804666519165</v>
       </c>
       <c r="L49" t="n">
-        <v>7.736233448982238</v>
+        <v>7.026419568061828</v>
       </c>
     </row>
     <row r="50">
@@ -4286,37 +4286,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>7.203696727752686</v>
+        <v>6.79683780670166</v>
       </c>
       <c r="C50" t="n">
-        <v>6.586723566055298</v>
+        <v>7.120046854019165</v>
       </c>
       <c r="D50" t="n">
-        <v>7.690761089324951</v>
+        <v>7.009780406951904</v>
       </c>
       <c r="E50" t="n">
-        <v>7.161833524703979</v>
+        <v>6.797361373901367</v>
       </c>
       <c r="F50" t="n">
-        <v>7.652531147003174</v>
+        <v>6.985851287841797</v>
       </c>
       <c r="G50" t="n">
-        <v>7.262532711029053</v>
+        <v>7.00530743598938</v>
       </c>
       <c r="H50" t="n">
-        <v>7.634894132614136</v>
+        <v>6.668179273605347</v>
       </c>
       <c r="I50" t="n">
-        <v>6.875125408172607</v>
+        <v>6.835280895233154</v>
       </c>
       <c r="J50" t="n">
-        <v>7.218260049819946</v>
+        <v>6.852713346481323</v>
       </c>
       <c r="K50" t="n">
-        <v>8.644561767578125</v>
+        <v>6.958805799484253</v>
       </c>
       <c r="L50" t="n">
-        <v>7.393092012405395</v>
+        <v>6.903016448020935</v>
       </c>
     </row>
     <row r="51">
@@ -4324,37 +4324,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>7.077638864517212</v>
+        <v>7.316863298416138</v>
       </c>
       <c r="C51" t="n">
-        <v>6.990832567214966</v>
+        <v>7.283003091812134</v>
       </c>
       <c r="D51" t="n">
-        <v>7.755362510681152</v>
+        <v>7.039146661758423</v>
       </c>
       <c r="E51" t="n">
-        <v>8.668279886245728</v>
+        <v>8.042419195175171</v>
       </c>
       <c r="F51" t="n">
-        <v>7.539346694946289</v>
+        <v>7.414831638336182</v>
       </c>
       <c r="G51" t="n">
-        <v>7.146309614181519</v>
+        <v>7.06812596321106</v>
       </c>
       <c r="H51" t="n">
-        <v>6.519921064376831</v>
+        <v>7.028780698776245</v>
       </c>
       <c r="I51" t="n">
-        <v>7.213655471801758</v>
+        <v>7.141978740692139</v>
       </c>
       <c r="J51" t="n">
-        <v>7.45754599571228</v>
+        <v>7.0068678855896</v>
       </c>
       <c r="K51" t="n">
-        <v>6.929857969284058</v>
+        <v>7.529964923858643</v>
       </c>
       <c r="L51" t="n">
-        <v>7.329875063896179</v>
+        <v>7.287198209762574</v>
       </c>
     </row>
     <row r="52">
@@ -4364,37 +4364,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>7.099815979003906</v>
+        <v>7.30812032699585</v>
       </c>
       <c r="C52" t="n">
-        <v>7.296068358421326</v>
+        <v>7.089493741989136</v>
       </c>
       <c r="D52" t="n">
-        <v>7.162622785568237</v>
+        <v>7.161785769462585</v>
       </c>
       <c r="E52" t="n">
-        <v>7.17675434589386</v>
+        <v>7.468428869247436</v>
       </c>
       <c r="F52" t="n">
-        <v>7.393038282394409</v>
+        <v>7.227280788421631</v>
       </c>
       <c r="G52" t="n">
-        <v>7.198340339660644</v>
+        <v>7.071241149902344</v>
       </c>
       <c r="H52" t="n">
-        <v>7.121511998176575</v>
+        <v>7.166578750610352</v>
       </c>
       <c r="I52" t="n">
-        <v>7.454187545776367</v>
+        <v>7.2206458568573</v>
       </c>
       <c r="J52" t="n">
-        <v>7.178234009742737</v>
+        <v>7.00595751285553</v>
       </c>
       <c r="K52" t="n">
-        <v>7.320033655166626</v>
+        <v>7.37141710281372</v>
       </c>
       <c r="L52" t="n">
-        <v>7.240060729980469</v>
+        <v>7.209094986915589</v>
       </c>
     </row>
   </sheetData>
